--- a/PN_2027/WBS_PN_2027_Equipamentos_Especiais.xlsx
+++ b/PN_2027/WBS_PN_2027_Equipamentos_Especiais.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cronograma" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curva orçamentária" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Premissas de prazo" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cronograma" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curva orçamentária" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Premissas de prazo" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +27,7 @@
     <numFmt numFmtId="167" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="168" formatCode="mmm/yy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,6 +46,11 @@
     <font>
       <i val="1"/>
       <color rgb="00628C0E"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F1F4C"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="4">
@@ -77,8 +83,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -86,7 +96,6 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -98,10 +107,8 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -515,7 +522,144 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PN 2027 - Obras DCMD - Instalação de Equipamentos Especiais (RL / RT / BC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GP: Sandro Padilha Dias Junior - DCMD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Projetos (SIGCO)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Blocos de instalação</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Religadores (RL)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Reguladores de tensão (RT)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Orçamento 2027 - curva 08/10 (R$)</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Curva orçamentária'!Q14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Orçamento base ago/26 (R$)</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>'Curva orçamentária'!R14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Primeira energização</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>46504</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Última energização</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>46630</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Último encerramento contábil</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>46644</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -530,83 +674,83 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>WBS</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Nome da tarefa</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Duração (dias)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Início</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Término</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>SIGCO</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>PN 2027 - Obras DCMD - Instalação de Equipamentos Especiais (RL / RT / BC)</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="6" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>BLOCO 1 - 90811 - LD UHE Isamu - Ponte Alta - 1UI1 - Instalação de 4 RL 34,5 kV</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="9" t="n">
         <v>46434</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="9" t="n">
         <v>46518</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="8" t="n">
         <v>90811</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
@@ -626,10 +770,10 @@
       <c r="C4" t="n">
         <v>30</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="4" t="n">
         <v>46434</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="4" t="n">
         <v>46464</v>
       </c>
       <c r="F4" t="n">
@@ -642,29 +786,29 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>1.1.2</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="11" t="n">
         <v>46464</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="11" t="n">
         <v>46464</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F5" s="10" t="n">
         <v>90811</v>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
@@ -684,10 +828,10 @@
       <c r="C6" t="n">
         <v>12</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="4" t="n">
         <v>46465</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="4" t="n">
         <v>46477</v>
       </c>
       <c r="F6" t="n">
@@ -713,10 +857,10 @@
       <c r="C7" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="4" t="n">
         <v>46478</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="4" t="n">
         <v>46488</v>
       </c>
       <c r="F7" t="n">
@@ -742,10 +886,10 @@
       <c r="C8" t="n">
         <v>15</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="4" t="n">
         <v>46489</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="4" t="n">
         <v>46504</v>
       </c>
       <c r="F8" t="n">
@@ -771,10 +915,10 @@
       <c r="C9" t="n">
         <v>8</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="4" t="n">
         <v>46489</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="4" t="n">
         <v>46497</v>
       </c>
       <c r="F9" t="n">
@@ -800,10 +944,10 @@
       <c r="C10" t="n">
         <v>15</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="4" t="n">
         <v>46489</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="4" t="n">
         <v>46504</v>
       </c>
       <c r="F10" t="n">
@@ -816,29 +960,29 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>1.1.8</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="11" t="n">
         <v>46504</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E11" s="11" t="n">
         <v>46504</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="10" t="n">
         <v>90811</v>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
@@ -858,10 +1002,10 @@
       <c r="C12" t="n">
         <v>7</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="4" t="n">
         <v>46505</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="4" t="n">
         <v>46513</v>
       </c>
       <c r="F12" t="n">
@@ -887,10 +1031,10 @@
       <c r="C13" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="4" t="n">
         <v>46514</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="4" t="n">
         <v>46518</v>
       </c>
       <c r="F13" t="n">
@@ -903,29 +1047,29 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>BLOCO 2 - 90811 - LD UHE Isamu - Ponte Alta - 1UI1 - Instalação de 3 RT 34,5 kV</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="9" t="n">
         <v>46434</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="9" t="n">
         <v>46518</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="8" t="n">
         <v>90811</v>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>RT</t>
         </is>
@@ -945,10 +1089,10 @@
       <c r="C15" t="n">
         <v>30</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="4" t="n">
         <v>46434</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="4" t="n">
         <v>46464</v>
       </c>
       <c r="F15" t="n">
@@ -961,29 +1105,29 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>1.2.2</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="11" t="n">
         <v>46464</v>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="E16" s="11" t="n">
         <v>46464</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="10" t="n">
         <v>90811</v>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>RT</t>
         </is>
@@ -1003,10 +1147,10 @@
       <c r="C17" t="n">
         <v>12</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="4" t="n">
         <v>46465</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="4" t="n">
         <v>46477</v>
       </c>
       <c r="F17" t="n">
@@ -1032,10 +1176,10 @@
       <c r="C18" t="n">
         <v>10</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="4" t="n">
         <v>46478</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="4" t="n">
         <v>46488</v>
       </c>
       <c r="F18" t="n">
@@ -1061,10 +1205,10 @@
       <c r="C19" t="n">
         <v>15</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="4" t="n">
         <v>46489</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E19" s="4" t="n">
         <v>46504</v>
       </c>
       <c r="F19" t="n">
@@ -1090,10 +1234,10 @@
       <c r="C20" t="n">
         <v>15</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="4" t="n">
         <v>46489</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="4" t="n">
         <v>46504</v>
       </c>
       <c r="F20" t="n">
@@ -1106,29 +1250,29 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>1.2.7</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="11" t="n">
         <v>46504</v>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="E21" s="11" t="n">
         <v>46504</v>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="F21" s="10" t="n">
         <v>90811</v>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>RT</t>
         </is>
@@ -1148,10 +1292,10 @@
       <c r="C22" t="n">
         <v>7</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="4" t="n">
         <v>46505</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="4" t="n">
         <v>46513</v>
       </c>
       <c r="F22" t="n">
@@ -1177,10 +1321,10 @@
       <c r="C23" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="4" t="n">
         <v>46514</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E23" s="4" t="n">
         <v>46518</v>
       </c>
       <c r="F23" t="n">
@@ -1193,29 +1337,29 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>BLOCO 3 - 89267 - LD Xambioá II - Araguanã - 2XB2 - Instalação de 2 RT 34,5 kV</t>
         </is>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="D24" s="5" t="n">
+      <c r="D24" s="9" t="n">
         <v>46462</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E24" s="9" t="n">
         <v>46546</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="8" t="n">
         <v>89267</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>RT</t>
         </is>
@@ -1235,10 +1379,10 @@
       <c r="C25" t="n">
         <v>30</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="4" t="n">
         <v>46462</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E25" s="4" t="n">
         <v>46492</v>
       </c>
       <c r="F25" t="n">
@@ -1251,29 +1395,29 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>1.3.2</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="8" t="n">
+      <c r="D26" s="11" t="n">
         <v>46492</v>
       </c>
-      <c r="E26" s="8" t="n">
+      <c r="E26" s="11" t="n">
         <v>46492</v>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="F26" s="10" t="n">
         <v>89267</v>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>RT</t>
         </is>
@@ -1293,10 +1437,10 @@
       <c r="C27" t="n">
         <v>12</v>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="4" t="n">
         <v>46493</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="E27" s="4" t="n">
         <v>46505</v>
       </c>
       <c r="F27" t="n">
@@ -1322,10 +1466,10 @@
       <c r="C28" t="n">
         <v>10</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="4" t="n">
         <v>46506</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="4" t="n">
         <v>46516</v>
       </c>
       <c r="F28" t="n">
@@ -1351,10 +1495,10 @@
       <c r="C29" t="n">
         <v>15</v>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="4" t="n">
         <v>46517</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="E29" s="4" t="n">
         <v>46532</v>
       </c>
       <c r="F29" t="n">
@@ -1380,10 +1524,10 @@
       <c r="C30" t="n">
         <v>15</v>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="4" t="n">
         <v>46517</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E30" s="4" t="n">
         <v>46532</v>
       </c>
       <c r="F30" t="n">
@@ -1396,29 +1540,29 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>1.3.7</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="8" t="n">
+      <c r="D31" s="11" t="n">
         <v>46532</v>
       </c>
-      <c r="E31" s="8" t="n">
+      <c r="E31" s="11" t="n">
         <v>46532</v>
       </c>
-      <c r="F31" s="7" t="n">
+      <c r="F31" s="10" t="n">
         <v>89267</v>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>RT</t>
         </is>
@@ -1438,10 +1582,10 @@
       <c r="C32" t="n">
         <v>7</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="4" t="n">
         <v>46533</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E32" s="4" t="n">
         <v>46541</v>
       </c>
       <c r="F32" t="n">
@@ -1467,10 +1611,10 @@
       <c r="C33" t="n">
         <v>3</v>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="4" t="n">
         <v>46542</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E33" s="4" t="n">
         <v>46546</v>
       </c>
       <c r="F33" t="n">
@@ -1483,29 +1627,29 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>BLOCO 4 - 91979 - QS-LD Gurupi - Duere - Instalação de 1 RL rural 34,5 kV + 3 TripSaver</t>
         </is>
       </c>
-      <c r="C34" s="4" t="n">
+      <c r="C34" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="D34" s="5" t="n">
+      <c r="D34" s="9" t="n">
         <v>46462</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E34" s="9" t="n">
         <v>46546</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="F34" s="8" t="n">
         <v>91979</v>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
@@ -1525,10 +1669,10 @@
       <c r="C35" t="n">
         <v>30</v>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="4" t="n">
         <v>46462</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="E35" s="4" t="n">
         <v>46492</v>
       </c>
       <c r="F35" t="n">
@@ -1541,29 +1685,29 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>1.4.2</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D36" s="8" t="n">
+      <c r="D36" s="11" t="n">
         <v>46492</v>
       </c>
-      <c r="E36" s="8" t="n">
+      <c r="E36" s="11" t="n">
         <v>46492</v>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="F36" s="10" t="n">
         <v>91979</v>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="G36" s="10" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
@@ -1583,10 +1727,10 @@
       <c r="C37" t="n">
         <v>12</v>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="4" t="n">
         <v>46493</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="E37" s="4" t="n">
         <v>46505</v>
       </c>
       <c r="F37" t="n">
@@ -1612,10 +1756,10 @@
       <c r="C38" t="n">
         <v>10</v>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="4" t="n">
         <v>46506</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="E38" s="4" t="n">
         <v>46516</v>
       </c>
       <c r="F38" t="n">
@@ -1641,10 +1785,10 @@
       <c r="C39" t="n">
         <v>15</v>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="4" t="n">
         <v>46517</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="E39" s="4" t="n">
         <v>46532</v>
       </c>
       <c r="F39" t="n">
@@ -1670,10 +1814,10 @@
       <c r="C40" t="n">
         <v>8</v>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="4" t="n">
         <v>46517</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="E40" s="4" t="n">
         <v>46525</v>
       </c>
       <c r="F40" t="n">
@@ -1699,10 +1843,10 @@
       <c r="C41" t="n">
         <v>15</v>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="4" t="n">
         <v>46517</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="E41" s="4" t="n">
         <v>46532</v>
       </c>
       <c r="F41" t="n">
@@ -1715,29 +1859,29 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>1.4.8</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D42" s="8" t="n">
+      <c r="D42" s="11" t="n">
         <v>46532</v>
       </c>
-      <c r="E42" s="8" t="n">
+      <c r="E42" s="11" t="n">
         <v>46532</v>
       </c>
-      <c r="F42" s="7" t="n">
+      <c r="F42" s="10" t="n">
         <v>91979</v>
       </c>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="G42" s="10" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
@@ -1757,10 +1901,10 @@
       <c r="C43" t="n">
         <v>7</v>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="4" t="n">
         <v>46533</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="E43" s="4" t="n">
         <v>46541</v>
       </c>
       <c r="F43" t="n">
@@ -1786,10 +1930,10 @@
       <c r="C44" t="n">
         <v>3</v>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="4" t="n">
         <v>46542</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="E44" s="4" t="n">
         <v>46546</v>
       </c>
       <c r="F44" t="n">
@@ -1802,29 +1946,29 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>BLOCO 5 - 92118 - QS-4 de Araguaína IV - Instalação de 1 RL 13,8 kV</t>
         </is>
       </c>
-      <c r="C45" s="4" t="n">
+      <c r="C45" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="D45" s="5" t="n">
+      <c r="D45" s="9" t="n">
         <v>46462</v>
       </c>
-      <c r="E45" s="5" t="n">
+      <c r="E45" s="9" t="n">
         <v>46546</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="F45" s="8" t="n">
         <v>92118</v>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G45" s="8" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
@@ -1844,10 +1988,10 @@
       <c r="C46" t="n">
         <v>30</v>
       </c>
-      <c r="D46" s="6" t="n">
+      <c r="D46" s="4" t="n">
         <v>46462</v>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="E46" s="4" t="n">
         <v>46492</v>
       </c>
       <c r="F46" t="n">
@@ -1860,29 +2004,29 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>1.5.2</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D47" s="8" t="n">
+      <c r="D47" s="11" t="n">
         <v>46492</v>
       </c>
-      <c r="E47" s="8" t="n">
+      <c r="E47" s="11" t="n">
         <v>46492</v>
       </c>
-      <c r="F47" s="7" t="n">
+      <c r="F47" s="10" t="n">
         <v>92118</v>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G47" s="10" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
@@ -1902,10 +2046,10 @@
       <c r="C48" t="n">
         <v>12</v>
       </c>
-      <c r="D48" s="6" t="n">
+      <c r="D48" s="4" t="n">
         <v>46493</v>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="E48" s="4" t="n">
         <v>46505</v>
       </c>
       <c r="F48" t="n">
@@ -1931,10 +2075,10 @@
       <c r="C49" t="n">
         <v>10</v>
       </c>
-      <c r="D49" s="6" t="n">
+      <c r="D49" s="4" t="n">
         <v>46506</v>
       </c>
-      <c r="E49" s="6" t="n">
+      <c r="E49" s="4" t="n">
         <v>46516</v>
       </c>
       <c r="F49" t="n">
@@ -1960,10 +2104,10 @@
       <c r="C50" t="n">
         <v>15</v>
       </c>
-      <c r="D50" s="6" t="n">
+      <c r="D50" s="4" t="n">
         <v>46517</v>
       </c>
-      <c r="E50" s="6" t="n">
+      <c r="E50" s="4" t="n">
         <v>46532</v>
       </c>
       <c r="F50" t="n">
@@ -1989,10 +2133,10 @@
       <c r="C51" t="n">
         <v>8</v>
       </c>
-      <c r="D51" s="6" t="n">
+      <c r="D51" s="4" t="n">
         <v>46517</v>
       </c>
-      <c r="E51" s="6" t="n">
+      <c r="E51" s="4" t="n">
         <v>46525</v>
       </c>
       <c r="F51" t="n">
@@ -2018,10 +2162,10 @@
       <c r="C52" t="n">
         <v>15</v>
       </c>
-      <c r="D52" s="6" t="n">
+      <c r="D52" s="4" t="n">
         <v>46517</v>
       </c>
-      <c r="E52" s="6" t="n">
+      <c r="E52" s="4" t="n">
         <v>46532</v>
       </c>
       <c r="F52" t="n">
@@ -2034,29 +2178,29 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>1.5.8</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="10" t="inlineStr">
         <is>
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D53" s="8" t="n">
+      <c r="D53" s="11" t="n">
         <v>46532</v>
       </c>
-      <c r="E53" s="8" t="n">
+      <c r="E53" s="11" t="n">
         <v>46532</v>
       </c>
-      <c r="F53" s="7" t="n">
+      <c r="F53" s="10" t="n">
         <v>92118</v>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="G53" s="10" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
@@ -2076,10 +2220,10 @@
       <c r="C54" t="n">
         <v>7</v>
       </c>
-      <c r="D54" s="6" t="n">
+      <c r="D54" s="4" t="n">
         <v>46533</v>
       </c>
-      <c r="E54" s="6" t="n">
+      <c r="E54" s="4" t="n">
         <v>46541</v>
       </c>
       <c r="F54" t="n">
@@ -2105,10 +2249,10 @@
       <c r="C55" t="n">
         <v>3</v>
       </c>
-      <c r="D55" s="6" t="n">
+      <c r="D55" s="4" t="n">
         <v>46542</v>
       </c>
-      <c r="E55" s="6" t="n">
+      <c r="E55" s="4" t="n">
         <v>46546</v>
       </c>
       <c r="F55" t="n">
@@ -2121,29 +2265,29 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>BLOCO 6 - 70838 - LD Cristalândia - Lagoa da Confusão - Instalação de 1 RT 34,5 kV</t>
         </is>
       </c>
-      <c r="C56" s="4" t="n">
+      <c r="C56" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="D56" s="5" t="n">
+      <c r="D56" s="9" t="n">
         <v>46497</v>
       </c>
-      <c r="E56" s="5" t="n">
+      <c r="E56" s="9" t="n">
         <v>46581</v>
       </c>
-      <c r="F56" s="4" t="n">
+      <c r="F56" s="8" t="n">
         <v>70838</v>
       </c>
-      <c r="G56" s="4" t="inlineStr">
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t>RT</t>
         </is>
@@ -2163,10 +2307,10 @@
       <c r="C57" t="n">
         <v>30</v>
       </c>
-      <c r="D57" s="6" t="n">
+      <c r="D57" s="4" t="n">
         <v>46497</v>
       </c>
-      <c r="E57" s="6" t="n">
+      <c r="E57" s="4" t="n">
         <v>46527</v>
       </c>
       <c r="F57" t="n">
@@ -2179,29 +2323,29 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="inlineStr">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>1.6.2</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D58" s="8" t="n">
+      <c r="D58" s="11" t="n">
         <v>46527</v>
       </c>
-      <c r="E58" s="8" t="n">
+      <c r="E58" s="11" t="n">
         <v>46527</v>
       </c>
-      <c r="F58" s="7" t="n">
+      <c r="F58" s="10" t="n">
         <v>70838</v>
       </c>
-      <c r="G58" s="7" t="inlineStr">
+      <c r="G58" s="10" t="inlineStr">
         <is>
           <t>RT</t>
         </is>
@@ -2221,10 +2365,10 @@
       <c r="C59" t="n">
         <v>12</v>
       </c>
-      <c r="D59" s="6" t="n">
+      <c r="D59" s="4" t="n">
         <v>46528</v>
       </c>
-      <c r="E59" s="6" t="n">
+      <c r="E59" s="4" t="n">
         <v>46540</v>
       </c>
       <c r="F59" t="n">
@@ -2250,10 +2394,10 @@
       <c r="C60" t="n">
         <v>10</v>
       </c>
-      <c r="D60" s="6" t="n">
+      <c r="D60" s="4" t="n">
         <v>46541</v>
       </c>
-      <c r="E60" s="6" t="n">
+      <c r="E60" s="4" t="n">
         <v>46551</v>
       </c>
       <c r="F60" t="n">
@@ -2279,10 +2423,10 @@
       <c r="C61" t="n">
         <v>15</v>
       </c>
-      <c r="D61" s="6" t="n">
+      <c r="D61" s="4" t="n">
         <v>46552</v>
       </c>
-      <c r="E61" s="6" t="n">
+      <c r="E61" s="4" t="n">
         <v>46567</v>
       </c>
       <c r="F61" t="n">
@@ -2308,10 +2452,10 @@
       <c r="C62" t="n">
         <v>15</v>
       </c>
-      <c r="D62" s="6" t="n">
+      <c r="D62" s="4" t="n">
         <v>46552</v>
       </c>
-      <c r="E62" s="6" t="n">
+      <c r="E62" s="4" t="n">
         <v>46567</v>
       </c>
       <c r="F62" t="n">
@@ -2324,29 +2468,29 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="inlineStr">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>1.6.7</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D63" s="8" t="n">
+      <c r="D63" s="11" t="n">
         <v>46567</v>
       </c>
-      <c r="E63" s="8" t="n">
+      <c r="E63" s="11" t="n">
         <v>46567</v>
       </c>
-      <c r="F63" s="7" t="n">
+      <c r="F63" s="10" t="n">
         <v>70838</v>
       </c>
-      <c r="G63" s="7" t="inlineStr">
+      <c r="G63" s="10" t="inlineStr">
         <is>
           <t>RT</t>
         </is>
@@ -2366,10 +2510,10 @@
       <c r="C64" t="n">
         <v>7</v>
       </c>
-      <c r="D64" s="6" t="n">
+      <c r="D64" s="4" t="n">
         <v>46568</v>
       </c>
-      <c r="E64" s="6" t="n">
+      <c r="E64" s="4" t="n">
         <v>46576</v>
       </c>
       <c r="F64" t="n">
@@ -2395,10 +2539,10 @@
       <c r="C65" t="n">
         <v>3</v>
       </c>
-      <c r="D65" s="6" t="n">
+      <c r="D65" s="4" t="n">
         <v>46577</v>
       </c>
-      <c r="E65" s="6" t="n">
+      <c r="E65" s="4" t="n">
         <v>46581</v>
       </c>
       <c r="F65" t="n">
@@ -2411,29 +2555,29 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>BLOCO 7 - 70978 - LD Paraíso I - Caseara - 2PR0 - Instalação de 1 RT 34,5 kV</t>
         </is>
       </c>
-      <c r="C66" s="4" t="n">
+      <c r="C66" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="D66" s="5" t="n">
+      <c r="D66" s="9" t="n">
         <v>46497</v>
       </c>
-      <c r="E66" s="5" t="n">
+      <c r="E66" s="9" t="n">
         <v>46581</v>
       </c>
-      <c r="F66" s="4" t="n">
+      <c r="F66" s="8" t="n">
         <v>70978</v>
       </c>
-      <c r="G66" s="4" t="inlineStr">
+      <c r="G66" s="8" t="inlineStr">
         <is>
           <t>RT</t>
         </is>
@@ -2453,10 +2597,10 @@
       <c r="C67" t="n">
         <v>30</v>
       </c>
-      <c r="D67" s="6" t="n">
+      <c r="D67" s="4" t="n">
         <v>46497</v>
       </c>
-      <c r="E67" s="6" t="n">
+      <c r="E67" s="4" t="n">
         <v>46527</v>
       </c>
       <c r="F67" t="n">
@@ -2469,29 +2613,29 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="7" t="inlineStr">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>1.7.2</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C68" s="7" t="n">
+      <c r="C68" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D68" s="8" t="n">
+      <c r="D68" s="11" t="n">
         <v>46527</v>
       </c>
-      <c r="E68" s="8" t="n">
+      <c r="E68" s="11" t="n">
         <v>46527</v>
       </c>
-      <c r="F68" s="7" t="n">
+      <c r="F68" s="10" t="n">
         <v>70978</v>
       </c>
-      <c r="G68" s="7" t="inlineStr">
+      <c r="G68" s="10" t="inlineStr">
         <is>
           <t>RT</t>
         </is>
@@ -2511,10 +2655,10 @@
       <c r="C69" t="n">
         <v>12</v>
       </c>
-      <c r="D69" s="6" t="n">
+      <c r="D69" s="4" t="n">
         <v>46528</v>
       </c>
-      <c r="E69" s="6" t="n">
+      <c r="E69" s="4" t="n">
         <v>46540</v>
       </c>
       <c r="F69" t="n">
@@ -2540,10 +2684,10 @@
       <c r="C70" t="n">
         <v>10</v>
       </c>
-      <c r="D70" s="6" t="n">
+      <c r="D70" s="4" t="n">
         <v>46541</v>
       </c>
-      <c r="E70" s="6" t="n">
+      <c r="E70" s="4" t="n">
         <v>46551</v>
       </c>
       <c r="F70" t="n">
@@ -2569,10 +2713,10 @@
       <c r="C71" t="n">
         <v>15</v>
       </c>
-      <c r="D71" s="6" t="n">
+      <c r="D71" s="4" t="n">
         <v>46552</v>
       </c>
-      <c r="E71" s="6" t="n">
+      <c r="E71" s="4" t="n">
         <v>46567</v>
       </c>
       <c r="F71" t="n">
@@ -2598,10 +2742,10 @@
       <c r="C72" t="n">
         <v>15</v>
       </c>
-      <c r="D72" s="6" t="n">
+      <c r="D72" s="4" t="n">
         <v>46552</v>
       </c>
-      <c r="E72" s="6" t="n">
+      <c r="E72" s="4" t="n">
         <v>46567</v>
       </c>
       <c r="F72" t="n">
@@ -2614,29 +2758,29 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="7" t="inlineStr">
+      <c r="A73" s="10" t="inlineStr">
         <is>
           <t>1.7.7</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
+      <c r="B73" s="10" t="inlineStr">
         <is>
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C73" s="7" t="n">
+      <c r="C73" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D73" s="8" t="n">
+      <c r="D73" s="11" t="n">
         <v>46567</v>
       </c>
-      <c r="E73" s="8" t="n">
+      <c r="E73" s="11" t="n">
         <v>46567</v>
       </c>
-      <c r="F73" s="7" t="n">
+      <c r="F73" s="10" t="n">
         <v>70978</v>
       </c>
-      <c r="G73" s="7" t="inlineStr">
+      <c r="G73" s="10" t="inlineStr">
         <is>
           <t>RT</t>
         </is>
@@ -2656,10 +2800,10 @@
       <c r="C74" t="n">
         <v>7</v>
       </c>
-      <c r="D74" s="6" t="n">
+      <c r="D74" s="4" t="n">
         <v>46568</v>
       </c>
-      <c r="E74" s="6" t="n">
+      <c r="E74" s="4" t="n">
         <v>46576</v>
       </c>
       <c r="F74" t="n">
@@ -2685,10 +2829,10 @@
       <c r="C75" t="n">
         <v>3</v>
       </c>
-      <c r="D75" s="6" t="n">
+      <c r="D75" s="4" t="n">
         <v>46577</v>
       </c>
-      <c r="E75" s="6" t="n">
+      <c r="E75" s="4" t="n">
         <v>46581</v>
       </c>
       <c r="F75" t="n">
@@ -2701,29 +2845,29 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="8" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>BLOCO 8 - 92094 - QS-LD Palmas - Aparecida do Rio Negro - Instalação de 3 RL 34,5 kV</t>
         </is>
       </c>
-      <c r="C76" s="4" t="n">
+      <c r="C76" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="D76" s="5" t="n">
+      <c r="D76" s="9" t="n">
         <v>46497</v>
       </c>
-      <c r="E76" s="5" t="n">
+      <c r="E76" s="9" t="n">
         <v>46581</v>
       </c>
-      <c r="F76" s="4" t="n">
+      <c r="F76" s="8" t="n">
         <v>92094</v>
       </c>
-      <c r="G76" s="4" t="inlineStr">
+      <c r="G76" s="8" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
@@ -2743,10 +2887,10 @@
       <c r="C77" t="n">
         <v>30</v>
       </c>
-      <c r="D77" s="6" t="n">
+      <c r="D77" s="4" t="n">
         <v>46497</v>
       </c>
-      <c r="E77" s="6" t="n">
+      <c r="E77" s="4" t="n">
         <v>46527</v>
       </c>
       <c r="F77" t="n">
@@ -2759,29 +2903,29 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="7" t="inlineStr">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>1.8.2</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B78" s="10" t="inlineStr">
         <is>
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C78" s="7" t="n">
+      <c r="C78" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D78" s="8" t="n">
+      <c r="D78" s="11" t="n">
         <v>46527</v>
       </c>
-      <c r="E78" s="8" t="n">
+      <c r="E78" s="11" t="n">
         <v>46527</v>
       </c>
-      <c r="F78" s="7" t="n">
+      <c r="F78" s="10" t="n">
         <v>92094</v>
       </c>
-      <c r="G78" s="7" t="inlineStr">
+      <c r="G78" s="10" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
@@ -2801,10 +2945,10 @@
       <c r="C79" t="n">
         <v>12</v>
       </c>
-      <c r="D79" s="6" t="n">
+      <c r="D79" s="4" t="n">
         <v>46528</v>
       </c>
-      <c r="E79" s="6" t="n">
+      <c r="E79" s="4" t="n">
         <v>46540</v>
       </c>
       <c r="F79" t="n">
@@ -2830,10 +2974,10 @@
       <c r="C80" t="n">
         <v>10</v>
       </c>
-      <c r="D80" s="6" t="n">
+      <c r="D80" s="4" t="n">
         <v>46541</v>
       </c>
-      <c r="E80" s="6" t="n">
+      <c r="E80" s="4" t="n">
         <v>46551</v>
       </c>
       <c r="F80" t="n">
@@ -2859,10 +3003,10 @@
       <c r="C81" t="n">
         <v>15</v>
       </c>
-      <c r="D81" s="6" t="n">
+      <c r="D81" s="4" t="n">
         <v>46552</v>
       </c>
-      <c r="E81" s="6" t="n">
+      <c r="E81" s="4" t="n">
         <v>46567</v>
       </c>
       <c r="F81" t="n">
@@ -2888,10 +3032,10 @@
       <c r="C82" t="n">
         <v>8</v>
       </c>
-      <c r="D82" s="6" t="n">
+      <c r="D82" s="4" t="n">
         <v>46552</v>
       </c>
-      <c r="E82" s="6" t="n">
+      <c r="E82" s="4" t="n">
         <v>46560</v>
       </c>
       <c r="F82" t="n">
@@ -2917,10 +3061,10 @@
       <c r="C83" t="n">
         <v>15</v>
       </c>
-      <c r="D83" s="6" t="n">
+      <c r="D83" s="4" t="n">
         <v>46552</v>
       </c>
-      <c r="E83" s="6" t="n">
+      <c r="E83" s="4" t="n">
         <v>46567</v>
       </c>
       <c r="F83" t="n">
@@ -2933,29 +3077,29 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="7" t="inlineStr">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>1.8.8</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
+      <c r="B84" s="10" t="inlineStr">
         <is>
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C84" s="7" t="n">
+      <c r="C84" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D84" s="8" t="n">
+      <c r="D84" s="11" t="n">
         <v>46567</v>
       </c>
-      <c r="E84" s="8" t="n">
+      <c r="E84" s="11" t="n">
         <v>46567</v>
       </c>
-      <c r="F84" s="7" t="n">
+      <c r="F84" s="10" t="n">
         <v>92094</v>
       </c>
-      <c r="G84" s="7" t="inlineStr">
+      <c r="G84" s="10" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
@@ -2975,10 +3119,10 @@
       <c r="C85" t="n">
         <v>7</v>
       </c>
-      <c r="D85" s="6" t="n">
+      <c r="D85" s="4" t="n">
         <v>46568</v>
       </c>
-      <c r="E85" s="6" t="n">
+      <c r="E85" s="4" t="n">
         <v>46576</v>
       </c>
       <c r="F85" t="n">
@@ -3004,10 +3148,10 @@
       <c r="C86" t="n">
         <v>3</v>
       </c>
-      <c r="D86" s="6" t="n">
+      <c r="D86" s="4" t="n">
         <v>46577</v>
       </c>
-      <c r="E86" s="6" t="n">
+      <c r="E86" s="4" t="n">
         <v>46581</v>
       </c>
       <c r="F86" t="n">
@@ -3020,29 +3164,29 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="A87" s="8" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>BLOCO 9 - 92095 - QS-LD Palmas - Lajeado - Instalação de 1 RL 34,5 kV</t>
         </is>
       </c>
-      <c r="C87" s="4" t="n">
+      <c r="C87" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="D87" s="5" t="n">
+      <c r="D87" s="9" t="n">
         <v>46497</v>
       </c>
-      <c r="E87" s="5" t="n">
+      <c r="E87" s="9" t="n">
         <v>46581</v>
       </c>
-      <c r="F87" s="4" t="n">
+      <c r="F87" s="8" t="n">
         <v>92095</v>
       </c>
-      <c r="G87" s="4" t="inlineStr">
+      <c r="G87" s="8" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
@@ -3062,10 +3206,10 @@
       <c r="C88" t="n">
         <v>30</v>
       </c>
-      <c r="D88" s="6" t="n">
+      <c r="D88" s="4" t="n">
         <v>46497</v>
       </c>
-      <c r="E88" s="6" t="n">
+      <c r="E88" s="4" t="n">
         <v>46527</v>
       </c>
       <c r="F88" t="n">
@@ -3078,29 +3222,29 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="7" t="inlineStr">
+      <c r="A89" s="10" t="inlineStr">
         <is>
           <t>1.9.2</t>
         </is>
       </c>
-      <c r="B89" s="7" t="inlineStr">
+      <c r="B89" s="10" t="inlineStr">
         <is>
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C89" s="7" t="n">
+      <c r="C89" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D89" s="8" t="n">
+      <c r="D89" s="11" t="n">
         <v>46527</v>
       </c>
-      <c r="E89" s="8" t="n">
+      <c r="E89" s="11" t="n">
         <v>46527</v>
       </c>
-      <c r="F89" s="7" t="n">
+      <c r="F89" s="10" t="n">
         <v>92095</v>
       </c>
-      <c r="G89" s="7" t="inlineStr">
+      <c r="G89" s="10" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
@@ -3120,10 +3264,10 @@
       <c r="C90" t="n">
         <v>12</v>
       </c>
-      <c r="D90" s="6" t="n">
+      <c r="D90" s="4" t="n">
         <v>46528</v>
       </c>
-      <c r="E90" s="6" t="n">
+      <c r="E90" s="4" t="n">
         <v>46540</v>
       </c>
       <c r="F90" t="n">
@@ -3149,10 +3293,10 @@
       <c r="C91" t="n">
         <v>10</v>
       </c>
-      <c r="D91" s="6" t="n">
+      <c r="D91" s="4" t="n">
         <v>46541</v>
       </c>
-      <c r="E91" s="6" t="n">
+      <c r="E91" s="4" t="n">
         <v>46551</v>
       </c>
       <c r="F91" t="n">
@@ -3178,10 +3322,10 @@
       <c r="C92" t="n">
         <v>15</v>
       </c>
-      <c r="D92" s="6" t="n">
+      <c r="D92" s="4" t="n">
         <v>46552</v>
       </c>
-      <c r="E92" s="6" t="n">
+      <c r="E92" s="4" t="n">
         <v>46567</v>
       </c>
       <c r="F92" t="n">
@@ -3207,10 +3351,10 @@
       <c r="C93" t="n">
         <v>8</v>
       </c>
-      <c r="D93" s="6" t="n">
+      <c r="D93" s="4" t="n">
         <v>46552</v>
       </c>
-      <c r="E93" s="6" t="n">
+      <c r="E93" s="4" t="n">
         <v>46560</v>
       </c>
       <c r="F93" t="n">
@@ -3236,10 +3380,10 @@
       <c r="C94" t="n">
         <v>15</v>
       </c>
-      <c r="D94" s="6" t="n">
+      <c r="D94" s="4" t="n">
         <v>46552</v>
       </c>
-      <c r="E94" s="6" t="n">
+      <c r="E94" s="4" t="n">
         <v>46567</v>
       </c>
       <c r="F94" t="n">
@@ -3252,29 +3396,29 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="7" t="inlineStr">
+      <c r="A95" s="10" t="inlineStr">
         <is>
           <t>1.9.8</t>
         </is>
       </c>
-      <c r="B95" s="7" t="inlineStr">
+      <c r="B95" s="10" t="inlineStr">
         <is>
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C95" s="7" t="n">
+      <c r="C95" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D95" s="8" t="n">
+      <c r="D95" s="11" t="n">
         <v>46567</v>
       </c>
-      <c r="E95" s="8" t="n">
+      <c r="E95" s="11" t="n">
         <v>46567</v>
       </c>
-      <c r="F95" s="7" t="n">
+      <c r="F95" s="10" t="n">
         <v>92095</v>
       </c>
-      <c r="G95" s="7" t="inlineStr">
+      <c r="G95" s="10" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
@@ -3294,10 +3438,10 @@
       <c r="C96" t="n">
         <v>7</v>
       </c>
-      <c r="D96" s="6" t="n">
+      <c r="D96" s="4" t="n">
         <v>46568</v>
       </c>
-      <c r="E96" s="6" t="n">
+      <c r="E96" s="4" t="n">
         <v>46576</v>
       </c>
       <c r="F96" t="n">
@@ -3323,10 +3467,10 @@
       <c r="C97" t="n">
         <v>3</v>
       </c>
-      <c r="D97" s="6" t="n">
+      <c r="D97" s="4" t="n">
         <v>46577</v>
       </c>
-      <c r="E97" s="6" t="n">
+      <c r="E97" s="4" t="n">
         <v>46581</v>
       </c>
       <c r="F97" t="n">
@@ -3339,29 +3483,29 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="inlineStr">
+      <c r="A98" s="8" t="inlineStr">
         <is>
           <t>1.10</t>
         </is>
       </c>
-      <c r="B98" s="4" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>BLOCO 10 - 92101 - QS-8 de Palmas IV - Instalação de 1 RL 13,8 kV</t>
         </is>
       </c>
-      <c r="C98" s="4" t="n">
+      <c r="C98" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="D98" s="5" t="n">
+      <c r="D98" s="9" t="n">
         <v>46497</v>
       </c>
-      <c r="E98" s="5" t="n">
+      <c r="E98" s="9" t="n">
         <v>46581</v>
       </c>
-      <c r="F98" s="4" t="n">
+      <c r="F98" s="8" t="n">
         <v>92101</v>
       </c>
-      <c r="G98" s="4" t="inlineStr">
+      <c r="G98" s="8" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
@@ -3381,10 +3525,10 @@
       <c r="C99" t="n">
         <v>30</v>
       </c>
-      <c r="D99" s="6" t="n">
+      <c r="D99" s="4" t="n">
         <v>46497</v>
       </c>
-      <c r="E99" s="6" t="n">
+      <c r="E99" s="4" t="n">
         <v>46527</v>
       </c>
       <c r="F99" t="n">
@@ -3397,29 +3541,29 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="7" t="inlineStr">
+      <c r="A100" s="10" t="inlineStr">
         <is>
           <t>1.10.2</t>
         </is>
       </c>
-      <c r="B100" s="7" t="inlineStr">
+      <c r="B100" s="10" t="inlineStr">
         <is>
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C100" s="7" t="n">
+      <c r="C100" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D100" s="8" t="n">
+      <c r="D100" s="11" t="n">
         <v>46527</v>
       </c>
-      <c r="E100" s="8" t="n">
+      <c r="E100" s="11" t="n">
         <v>46527</v>
       </c>
-      <c r="F100" s="7" t="n">
+      <c r="F100" s="10" t="n">
         <v>92101</v>
       </c>
-      <c r="G100" s="7" t="inlineStr">
+      <c r="G100" s="10" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
@@ -3439,10 +3583,10 @@
       <c r="C101" t="n">
         <v>12</v>
       </c>
-      <c r="D101" s="6" t="n">
+      <c r="D101" s="4" t="n">
         <v>46528</v>
       </c>
-      <c r="E101" s="6" t="n">
+      <c r="E101" s="4" t="n">
         <v>46540</v>
       </c>
       <c r="F101" t="n">
@@ -3468,10 +3612,10 @@
       <c r="C102" t="n">
         <v>10</v>
       </c>
-      <c r="D102" s="6" t="n">
+      <c r="D102" s="4" t="n">
         <v>46541</v>
       </c>
-      <c r="E102" s="6" t="n">
+      <c r="E102" s="4" t="n">
         <v>46551</v>
       </c>
       <c r="F102" t="n">
@@ -3497,10 +3641,10 @@
       <c r="C103" t="n">
         <v>15</v>
       </c>
-      <c r="D103" s="6" t="n">
+      <c r="D103" s="4" t="n">
         <v>46552</v>
       </c>
-      <c r="E103" s="6" t="n">
+      <c r="E103" s="4" t="n">
         <v>46567</v>
       </c>
       <c r="F103" t="n">
@@ -3526,10 +3670,10 @@
       <c r="C104" t="n">
         <v>8</v>
       </c>
-      <c r="D104" s="6" t="n">
+      <c r="D104" s="4" t="n">
         <v>46552</v>
       </c>
-      <c r="E104" s="6" t="n">
+      <c r="E104" s="4" t="n">
         <v>46560</v>
       </c>
       <c r="F104" t="n">
@@ -3555,10 +3699,10 @@
       <c r="C105" t="n">
         <v>15</v>
       </c>
-      <c r="D105" s="6" t="n">
+      <c r="D105" s="4" t="n">
         <v>46552</v>
       </c>
-      <c r="E105" s="6" t="n">
+      <c r="E105" s="4" t="n">
         <v>46567</v>
       </c>
       <c r="F105" t="n">
@@ -3571,29 +3715,29 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="7" t="inlineStr">
+      <c r="A106" s="10" t="inlineStr">
         <is>
           <t>1.10.8</t>
         </is>
       </c>
-      <c r="B106" s="7" t="inlineStr">
+      <c r="B106" s="10" t="inlineStr">
         <is>
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C106" s="7" t="n">
+      <c r="C106" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D106" s="8" t="n">
+      <c r="D106" s="11" t="n">
         <v>46567</v>
       </c>
-      <c r="E106" s="8" t="n">
+      <c r="E106" s="11" t="n">
         <v>46567</v>
       </c>
-      <c r="F106" s="7" t="n">
+      <c r="F106" s="10" t="n">
         <v>92101</v>
       </c>
-      <c r="G106" s="7" t="inlineStr">
+      <c r="G106" s="10" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
@@ -3613,10 +3757,10 @@
       <c r="C107" t="n">
         <v>7</v>
       </c>
-      <c r="D107" s="6" t="n">
+      <c r="D107" s="4" t="n">
         <v>46568</v>
       </c>
-      <c r="E107" s="6" t="n">
+      <c r="E107" s="4" t="n">
         <v>46576</v>
       </c>
       <c r="F107" t="n">
@@ -3642,10 +3786,10 @@
       <c r="C108" t="n">
         <v>3</v>
       </c>
-      <c r="D108" s="6" t="n">
+      <c r="D108" s="4" t="n">
         <v>46577</v>
       </c>
-      <c r="E108" s="6" t="n">
+      <c r="E108" s="4" t="n">
         <v>46581</v>
       </c>
       <c r="F108" t="n">
@@ -3658,29 +3802,29 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr">
+      <c r="A109" s="8" t="inlineStr">
         <is>
           <t>1.11</t>
         </is>
       </c>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>BLOCO 11 - 92102 - QS-6 de Palmas IV - Instalação de 1 RL 13,8 kV</t>
         </is>
       </c>
-      <c r="C109" s="4" t="n">
+      <c r="C109" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="D109" s="5" t="n">
+      <c r="D109" s="9" t="n">
         <v>46497</v>
       </c>
-      <c r="E109" s="5" t="n">
+      <c r="E109" s="9" t="n">
         <v>46581</v>
       </c>
-      <c r="F109" s="4" t="n">
+      <c r="F109" s="8" t="n">
         <v>92102</v>
       </c>
-      <c r="G109" s="4" t="inlineStr">
+      <c r="G109" s="8" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
@@ -3700,10 +3844,10 @@
       <c r="C110" t="n">
         <v>30</v>
       </c>
-      <c r="D110" s="6" t="n">
+      <c r="D110" s="4" t="n">
         <v>46497</v>
       </c>
-      <c r="E110" s="6" t="n">
+      <c r="E110" s="4" t="n">
         <v>46527</v>
       </c>
       <c r="F110" t="n">
@@ -3716,29 +3860,29 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="7" t="inlineStr">
+      <c r="A111" s="10" t="inlineStr">
         <is>
           <t>1.11.2</t>
         </is>
       </c>
-      <c r="B111" s="7" t="inlineStr">
+      <c r="B111" s="10" t="inlineStr">
         <is>
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C111" s="7" t="n">
+      <c r="C111" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D111" s="8" t="n">
+      <c r="D111" s="11" t="n">
         <v>46527</v>
       </c>
-      <c r="E111" s="8" t="n">
+      <c r="E111" s="11" t="n">
         <v>46527</v>
       </c>
-      <c r="F111" s="7" t="n">
+      <c r="F111" s="10" t="n">
         <v>92102</v>
       </c>
-      <c r="G111" s="7" t="inlineStr">
+      <c r="G111" s="10" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
@@ -3758,10 +3902,10 @@
       <c r="C112" t="n">
         <v>12</v>
       </c>
-      <c r="D112" s="6" t="n">
+      <c r="D112" s="4" t="n">
         <v>46528</v>
       </c>
-      <c r="E112" s="6" t="n">
+      <c r="E112" s="4" t="n">
         <v>46540</v>
       </c>
       <c r="F112" t="n">
@@ -3787,10 +3931,10 @@
       <c r="C113" t="n">
         <v>10</v>
       </c>
-      <c r="D113" s="6" t="n">
+      <c r="D113" s="4" t="n">
         <v>46541</v>
       </c>
-      <c r="E113" s="6" t="n">
+      <c r="E113" s="4" t="n">
         <v>46551</v>
       </c>
       <c r="F113" t="n">
@@ -3816,10 +3960,10 @@
       <c r="C114" t="n">
         <v>15</v>
       </c>
-      <c r="D114" s="6" t="n">
+      <c r="D114" s="4" t="n">
         <v>46552</v>
       </c>
-      <c r="E114" s="6" t="n">
+      <c r="E114" s="4" t="n">
         <v>46567</v>
       </c>
       <c r="F114" t="n">
@@ -3845,10 +3989,10 @@
       <c r="C115" t="n">
         <v>8</v>
       </c>
-      <c r="D115" s="6" t="n">
+      <c r="D115" s="4" t="n">
         <v>46552</v>
       </c>
-      <c r="E115" s="6" t="n">
+      <c r="E115" s="4" t="n">
         <v>46560</v>
       </c>
       <c r="F115" t="n">
@@ -3874,10 +4018,10 @@
       <c r="C116" t="n">
         <v>15</v>
       </c>
-      <c r="D116" s="6" t="n">
+      <c r="D116" s="4" t="n">
         <v>46552</v>
       </c>
-      <c r="E116" s="6" t="n">
+      <c r="E116" s="4" t="n">
         <v>46567</v>
       </c>
       <c r="F116" t="n">
@@ -3890,29 +4034,29 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="7" t="inlineStr">
+      <c r="A117" s="10" t="inlineStr">
         <is>
           <t>1.11.8</t>
         </is>
       </c>
-      <c r="B117" s="7" t="inlineStr">
+      <c r="B117" s="10" t="inlineStr">
         <is>
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C117" s="7" t="n">
+      <c r="C117" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D117" s="8" t="n">
+      <c r="D117" s="11" t="n">
         <v>46567</v>
       </c>
-      <c r="E117" s="8" t="n">
+      <c r="E117" s="11" t="n">
         <v>46567</v>
       </c>
-      <c r="F117" s="7" t="n">
+      <c r="F117" s="10" t="n">
         <v>92102</v>
       </c>
-      <c r="G117" s="7" t="inlineStr">
+      <c r="G117" s="10" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
@@ -3932,10 +4076,10 @@
       <c r="C118" t="n">
         <v>7</v>
       </c>
-      <c r="D118" s="6" t="n">
+      <c r="D118" s="4" t="n">
         <v>46568</v>
       </c>
-      <c r="E118" s="6" t="n">
+      <c r="E118" s="4" t="n">
         <v>46576</v>
       </c>
       <c r="F118" t="n">
@@ -3961,10 +4105,10 @@
       <c r="C119" t="n">
         <v>3</v>
       </c>
-      <c r="D119" s="6" t="n">
+      <c r="D119" s="4" t="n">
         <v>46577</v>
       </c>
-      <c r="E119" s="6" t="n">
+      <c r="E119" s="4" t="n">
         <v>46581</v>
       </c>
       <c r="F119" t="n">
@@ -3977,29 +4121,29 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="4" t="inlineStr">
+      <c r="A120" s="8" t="inlineStr">
         <is>
           <t>1.12</t>
         </is>
       </c>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="B120" s="8" t="inlineStr">
         <is>
           <t>BLOCO 12 - 89249 - LD Araguaína - Babaçulândia - 2AR0 - Instalação de 1 RT 34,5 kV</t>
         </is>
       </c>
-      <c r="C120" s="4" t="n">
+      <c r="C120" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="D120" s="5" t="n">
+      <c r="D120" s="9" t="n">
         <v>46560</v>
       </c>
-      <c r="E120" s="5" t="n">
+      <c r="E120" s="9" t="n">
         <v>46644</v>
       </c>
-      <c r="F120" s="4" t="n">
+      <c r="F120" s="8" t="n">
         <v>89249</v>
       </c>
-      <c r="G120" s="4" t="inlineStr">
+      <c r="G120" s="8" t="inlineStr">
         <is>
           <t>RT</t>
         </is>
@@ -4019,10 +4163,10 @@
       <c r="C121" t="n">
         <v>30</v>
       </c>
-      <c r="D121" s="6" t="n">
+      <c r="D121" s="4" t="n">
         <v>46560</v>
       </c>
-      <c r="E121" s="6" t="n">
+      <c r="E121" s="4" t="n">
         <v>46590</v>
       </c>
       <c r="F121" t="n">
@@ -4035,29 +4179,29 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="7" t="inlineStr">
+      <c r="A122" s="10" t="inlineStr">
         <is>
           <t>1.12.2</t>
         </is>
       </c>
-      <c r="B122" s="7" t="inlineStr">
+      <c r="B122" s="10" t="inlineStr">
         <is>
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C122" s="7" t="n">
+      <c r="C122" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D122" s="8" t="n">
+      <c r="D122" s="11" t="n">
         <v>46590</v>
       </c>
-      <c r="E122" s="8" t="n">
+      <c r="E122" s="11" t="n">
         <v>46590</v>
       </c>
-      <c r="F122" s="7" t="n">
+      <c r="F122" s="10" t="n">
         <v>89249</v>
       </c>
-      <c r="G122" s="7" t="inlineStr">
+      <c r="G122" s="10" t="inlineStr">
         <is>
           <t>RT</t>
         </is>
@@ -4077,10 +4221,10 @@
       <c r="C123" t="n">
         <v>12</v>
       </c>
-      <c r="D123" s="6" t="n">
+      <c r="D123" s="4" t="n">
         <v>46591</v>
       </c>
-      <c r="E123" s="6" t="n">
+      <c r="E123" s="4" t="n">
         <v>46603</v>
       </c>
       <c r="F123" t="n">
@@ -4106,10 +4250,10 @@
       <c r="C124" t="n">
         <v>10</v>
       </c>
-      <c r="D124" s="6" t="n">
+      <c r="D124" s="4" t="n">
         <v>46604</v>
       </c>
-      <c r="E124" s="6" t="n">
+      <c r="E124" s="4" t="n">
         <v>46614</v>
       </c>
       <c r="F124" t="n">
@@ -4135,10 +4279,10 @@
       <c r="C125" t="n">
         <v>15</v>
       </c>
-      <c r="D125" s="6" t="n">
+      <c r="D125" s="4" t="n">
         <v>46615</v>
       </c>
-      <c r="E125" s="6" t="n">
+      <c r="E125" s="4" t="n">
         <v>46630</v>
       </c>
       <c r="F125" t="n">
@@ -4164,10 +4308,10 @@
       <c r="C126" t="n">
         <v>15</v>
       </c>
-      <c r="D126" s="6" t="n">
+      <c r="D126" s="4" t="n">
         <v>46615</v>
       </c>
-      <c r="E126" s="6" t="n">
+      <c r="E126" s="4" t="n">
         <v>46630</v>
       </c>
       <c r="F126" t="n">
@@ -4180,29 +4324,29 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="7" t="inlineStr">
+      <c r="A127" s="10" t="inlineStr">
         <is>
           <t>1.12.7</t>
         </is>
       </c>
-      <c r="B127" s="7" t="inlineStr">
+      <c r="B127" s="10" t="inlineStr">
         <is>
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C127" s="7" t="n">
+      <c r="C127" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D127" s="8" t="n">
+      <c r="D127" s="11" t="n">
         <v>46630</v>
       </c>
-      <c r="E127" s="8" t="n">
+      <c r="E127" s="11" t="n">
         <v>46630</v>
       </c>
-      <c r="F127" s="7" t="n">
+      <c r="F127" s="10" t="n">
         <v>89249</v>
       </c>
-      <c r="G127" s="7" t="inlineStr">
+      <c r="G127" s="10" t="inlineStr">
         <is>
           <t>RT</t>
         </is>
@@ -4222,10 +4366,10 @@
       <c r="C128" t="n">
         <v>7</v>
       </c>
-      <c r="D128" s="6" t="n">
+      <c r="D128" s="4" t="n">
         <v>46631</v>
       </c>
-      <c r="E128" s="6" t="n">
+      <c r="E128" s="4" t="n">
         <v>46639</v>
       </c>
       <c r="F128" t="n">
@@ -4251,10 +4395,10 @@
       <c r="C129" t="n">
         <v>3</v>
       </c>
-      <c r="D129" s="6" t="n">
+      <c r="D129" s="4" t="n">
         <v>46640</v>
       </c>
-      <c r="E129" s="6" t="n">
+      <c r="E129" s="4" t="n">
         <v>46644</v>
       </c>
       <c r="F129" t="n">
@@ -4267,29 +4411,29 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="4" t="inlineStr">
+      <c r="A130" s="8" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="B130" s="4" t="inlineStr">
+      <c r="B130" s="8" t="inlineStr">
         <is>
           <t>BLOCO 13 - 89307 - 1 de Figueirópolis - 2FGR - Instalação de 1 RT 13,8 kV + remanejamento de 1 RL</t>
         </is>
       </c>
-      <c r="C130" s="4" t="n">
+      <c r="C130" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="D130" s="5" t="n">
+      <c r="D130" s="9" t="n">
         <v>46560</v>
       </c>
-      <c r="E130" s="5" t="n">
+      <c r="E130" s="9" t="n">
         <v>46644</v>
       </c>
-      <c r="F130" s="4" t="n">
+      <c r="F130" s="8" t="n">
         <v>89307</v>
       </c>
-      <c r="G130" s="4" t="inlineStr">
+      <c r="G130" s="8" t="inlineStr">
         <is>
           <t>RT</t>
         </is>
@@ -4309,10 +4453,10 @@
       <c r="C131" t="n">
         <v>30</v>
       </c>
-      <c r="D131" s="6" t="n">
+      <c r="D131" s="4" t="n">
         <v>46560</v>
       </c>
-      <c r="E131" s="6" t="n">
+      <c r="E131" s="4" t="n">
         <v>46590</v>
       </c>
       <c r="F131" t="n">
@@ -4325,29 +4469,29 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="7" t="inlineStr">
+      <c r="A132" s="10" t="inlineStr">
         <is>
           <t>1.13.2</t>
         </is>
       </c>
-      <c r="B132" s="7" t="inlineStr">
+      <c r="B132" s="10" t="inlineStr">
         <is>
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C132" s="7" t="n">
+      <c r="C132" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D132" s="8" t="n">
+      <c r="D132" s="11" t="n">
         <v>46590</v>
       </c>
-      <c r="E132" s="8" t="n">
+      <c r="E132" s="11" t="n">
         <v>46590</v>
       </c>
-      <c r="F132" s="7" t="n">
+      <c r="F132" s="10" t="n">
         <v>89307</v>
       </c>
-      <c r="G132" s="7" t="inlineStr">
+      <c r="G132" s="10" t="inlineStr">
         <is>
           <t>RT</t>
         </is>
@@ -4367,10 +4511,10 @@
       <c r="C133" t="n">
         <v>12</v>
       </c>
-      <c r="D133" s="6" t="n">
+      <c r="D133" s="4" t="n">
         <v>46591</v>
       </c>
-      <c r="E133" s="6" t="n">
+      <c r="E133" s="4" t="n">
         <v>46603</v>
       </c>
       <c r="F133" t="n">
@@ -4396,10 +4540,10 @@
       <c r="C134" t="n">
         <v>10</v>
       </c>
-      <c r="D134" s="6" t="n">
+      <c r="D134" s="4" t="n">
         <v>46604</v>
       </c>
-      <c r="E134" s="6" t="n">
+      <c r="E134" s="4" t="n">
         <v>46614</v>
       </c>
       <c r="F134" t="n">
@@ -4425,10 +4569,10 @@
       <c r="C135" t="n">
         <v>15</v>
       </c>
-      <c r="D135" s="6" t="n">
+      <c r="D135" s="4" t="n">
         <v>46615</v>
       </c>
-      <c r="E135" s="6" t="n">
+      <c r="E135" s="4" t="n">
         <v>46630</v>
       </c>
       <c r="F135" t="n">
@@ -4454,10 +4598,10 @@
       <c r="C136" t="n">
         <v>8</v>
       </c>
-      <c r="D136" s="6" t="n">
+      <c r="D136" s="4" t="n">
         <v>46615</v>
       </c>
-      <c r="E136" s="6" t="n">
+      <c r="E136" s="4" t="n">
         <v>46623</v>
       </c>
       <c r="F136" t="n">
@@ -4483,10 +4627,10 @@
       <c r="C137" t="n">
         <v>15</v>
       </c>
-      <c r="D137" s="6" t="n">
+      <c r="D137" s="4" t="n">
         <v>46615</v>
       </c>
-      <c r="E137" s="6" t="n">
+      <c r="E137" s="4" t="n">
         <v>46630</v>
       </c>
       <c r="F137" t="n">
@@ -4499,29 +4643,29 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="7" t="inlineStr">
+      <c r="A138" s="10" t="inlineStr">
         <is>
           <t>1.13.8</t>
         </is>
       </c>
-      <c r="B138" s="7" t="inlineStr">
+      <c r="B138" s="10" t="inlineStr">
         <is>
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C138" s="7" t="n">
+      <c r="C138" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D138" s="8" t="n">
+      <c r="D138" s="11" t="n">
         <v>46630</v>
       </c>
-      <c r="E138" s="8" t="n">
+      <c r="E138" s="11" t="n">
         <v>46630</v>
       </c>
-      <c r="F138" s="7" t="n">
+      <c r="F138" s="10" t="n">
         <v>89307</v>
       </c>
-      <c r="G138" s="7" t="inlineStr">
+      <c r="G138" s="10" t="inlineStr">
         <is>
           <t>RT</t>
         </is>
@@ -4541,10 +4685,10 @@
       <c r="C139" t="n">
         <v>7</v>
       </c>
-      <c r="D139" s="6" t="n">
+      <c r="D139" s="4" t="n">
         <v>46631</v>
       </c>
-      <c r="E139" s="6" t="n">
+      <c r="E139" s="4" t="n">
         <v>46639</v>
       </c>
       <c r="F139" t="n">
@@ -4570,10 +4714,10 @@
       <c r="C140" t="n">
         <v>3</v>
       </c>
-      <c r="D140" s="6" t="n">
+      <c r="D140" s="4" t="n">
         <v>46640</v>
       </c>
-      <c r="E140" s="6" t="n">
+      <c r="E140" s="4" t="n">
         <v>46644</v>
       </c>
       <c r="F140" t="n">
@@ -4587,14 +4731,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AL139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4640,144 +4785,144 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>WBS</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Início</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Término</t>
         </is>
       </c>
-      <c r="E1" s="9" t="n">
+      <c r="E1" s="12" t="n">
         <v>46426</v>
       </c>
-      <c r="F1" s="9" t="n">
+      <c r="F1" s="12" t="n">
         <v>46433</v>
       </c>
-      <c r="G1" s="9" t="n">
+      <c r="G1" s="12" t="n">
         <v>46440</v>
       </c>
-      <c r="H1" s="9" t="n">
+      <c r="H1" s="12" t="n">
         <v>46447</v>
       </c>
-      <c r="I1" s="9" t="n">
+      <c r="I1" s="12" t="n">
         <v>46454</v>
       </c>
-      <c r="J1" s="9" t="n">
+      <c r="J1" s="12" t="n">
         <v>46461</v>
       </c>
-      <c r="K1" s="9" t="n">
+      <c r="K1" s="12" t="n">
         <v>46468</v>
       </c>
-      <c r="L1" s="9" t="n">
+      <c r="L1" s="12" t="n">
         <v>46475</v>
       </c>
-      <c r="M1" s="9" t="n">
+      <c r="M1" s="12" t="n">
         <v>46482</v>
       </c>
-      <c r="N1" s="9" t="n">
+      <c r="N1" s="12" t="n">
         <v>46489</v>
       </c>
-      <c r="O1" s="9" t="n">
+      <c r="O1" s="12" t="n">
         <v>46496</v>
       </c>
-      <c r="P1" s="9" t="n">
+      <c r="P1" s="12" t="n">
         <v>46503</v>
       </c>
-      <c r="Q1" s="9" t="n">
+      <c r="Q1" s="12" t="n">
         <v>46510</v>
       </c>
-      <c r="R1" s="9" t="n">
+      <c r="R1" s="12" t="n">
         <v>46517</v>
       </c>
-      <c r="S1" s="9" t="n">
+      <c r="S1" s="12" t="n">
         <v>46524</v>
       </c>
-      <c r="T1" s="9" t="n">
+      <c r="T1" s="12" t="n">
         <v>46531</v>
       </c>
-      <c r="U1" s="9" t="n">
+      <c r="U1" s="12" t="n">
         <v>46538</v>
       </c>
-      <c r="V1" s="9" t="n">
+      <c r="V1" s="12" t="n">
         <v>46545</v>
       </c>
-      <c r="W1" s="9" t="n">
+      <c r="W1" s="12" t="n">
         <v>46552</v>
       </c>
-      <c r="X1" s="9" t="n">
+      <c r="X1" s="12" t="n">
         <v>46559</v>
       </c>
-      <c r="Y1" s="9" t="n">
+      <c r="Y1" s="12" t="n">
         <v>46566</v>
       </c>
-      <c r="Z1" s="9" t="n">
+      <c r="Z1" s="12" t="n">
         <v>46573</v>
       </c>
-      <c r="AA1" s="9" t="n">
+      <c r="AA1" s="12" t="n">
         <v>46580</v>
       </c>
-      <c r="AB1" s="9" t="n">
+      <c r="AB1" s="12" t="n">
         <v>46587</v>
       </c>
-      <c r="AC1" s="9" t="n">
+      <c r="AC1" s="12" t="n">
         <v>46594</v>
       </c>
-      <c r="AD1" s="9" t="n">
+      <c r="AD1" s="12" t="n">
         <v>46601</v>
       </c>
-      <c r="AE1" s="9" t="n">
+      <c r="AE1" s="12" t="n">
         <v>46608</v>
       </c>
-      <c r="AF1" s="9" t="n">
+      <c r="AF1" s="12" t="n">
         <v>46615</v>
       </c>
-      <c r="AG1" s="9" t="n">
+      <c r="AG1" s="12" t="n">
         <v>46622</v>
       </c>
-      <c r="AH1" s="9" t="n">
+      <c r="AH1" s="12" t="n">
         <v>46629</v>
       </c>
-      <c r="AI1" s="9" t="n">
+      <c r="AI1" s="12" t="n">
         <v>46636</v>
       </c>
-      <c r="AJ1" s="9" t="n">
+      <c r="AJ1" s="12" t="n">
         <v>46643</v>
       </c>
-      <c r="AK1" s="9" t="n">
+      <c r="AK1" s="12" t="n">
         <v>46650</v>
       </c>
-      <c r="AL1" s="9" t="n">
+      <c r="AL1" s="12" t="n">
         <v>46657</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>BLOCO 1 - 90811 - LD UHE Isamu - Ponte Alta - 1UI1 - Instalação de 4 RL 34,5 kV</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n">
+      <c r="C2" s="13" t="n">
         <v>46434</v>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="D2" s="13" t="n">
         <v>46518</v>
       </c>
     </row>
@@ -4792,10 +4937,10 @@
           <t>Executar Obras</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" s="14" t="n">
         <v>46434</v>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D3" s="14" t="n">
         <v>46464</v>
       </c>
     </row>
@@ -4810,10 +4955,10 @@
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" s="14" t="n">
         <v>46464</v>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="14" t="n">
         <v>46464</v>
       </c>
     </row>
@@ -4828,10 +4973,10 @@
           <t>Fiscalização</t>
         </is>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="14" t="n">
         <v>46465</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="14" t="n">
         <v>46477</v>
       </c>
     </row>
@@ -4846,10 +4991,10 @@
           <t>Cadastro EO / Integração parcial</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="14" t="n">
         <v>46478</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="14" t="n">
         <v>46488</v>
       </c>
     </row>
@@ -4864,10 +5009,10 @@
           <t>Entrega do TCI pela empreiteira / Integração final</t>
         </is>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="14" t="n">
         <v>46489</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="14" t="n">
         <v>46504</v>
       </c>
     </row>
@@ -4882,10 +5027,10 @@
           <t>Abertura de chamado / Atendimento GAT</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="14" t="n">
         <v>46489</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="14" t="n">
         <v>46497</v>
       </c>
     </row>
@@ -4900,10 +5045,10 @@
           <t>Comissionar Equipamentos</t>
         </is>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="14" t="n">
         <v>46489</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="14" t="n">
         <v>46504</v>
       </c>
     </row>
@@ -4918,10 +5063,10 @@
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="14" t="n">
         <v>46504</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="14" t="n">
         <v>46504</v>
       </c>
     </row>
@@ -4936,10 +5081,10 @@
           <t>Encerramento Técnico</t>
         </is>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="14" t="n">
         <v>46505</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="14" t="n">
         <v>46513</v>
       </c>
     </row>
@@ -4954,28 +5099,28 @@
           <t>Encerramento Contábil</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="14" t="n">
         <v>46514</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="14" t="n">
         <v>46518</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>BLOCO 2 - 90811 - LD UHE Isamu - Ponte Alta - 1UI1 - Instalação de 3 RT 34,5 kV</t>
         </is>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="13" t="n">
         <v>46434</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="13" t="n">
         <v>46518</v>
       </c>
     </row>
@@ -4990,10 +5135,10 @@
           <t>Executar Obras</t>
         </is>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="14" t="n">
         <v>46434</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="14" t="n">
         <v>46464</v>
       </c>
     </row>
@@ -5008,10 +5153,10 @@
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" s="14" t="n">
         <v>46464</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="14" t="n">
         <v>46464</v>
       </c>
     </row>
@@ -5026,10 +5171,10 @@
           <t>Fiscalização</t>
         </is>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C16" s="14" t="n">
         <v>46465</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="14" t="n">
         <v>46477</v>
       </c>
     </row>
@@ -5044,10 +5189,10 @@
           <t>Cadastro EO / Integração parcial</t>
         </is>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="14" t="n">
         <v>46478</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="14" t="n">
         <v>46488</v>
       </c>
     </row>
@@ -5062,10 +5207,10 @@
           <t>Entrega do TCI pela empreiteira / Integração final</t>
         </is>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C18" s="14" t="n">
         <v>46489</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="14" t="n">
         <v>46504</v>
       </c>
     </row>
@@ -5080,10 +5225,10 @@
           <t>Comissionar Equipamentos</t>
         </is>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="14" t="n">
         <v>46489</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="14" t="n">
         <v>46504</v>
       </c>
     </row>
@@ -5098,10 +5243,10 @@
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C20" s="11" t="n">
+      <c r="C20" s="14" t="n">
         <v>46504</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="14" t="n">
         <v>46504</v>
       </c>
     </row>
@@ -5116,10 +5261,10 @@
           <t>Encerramento Técnico</t>
         </is>
       </c>
-      <c r="C21" s="11" t="n">
+      <c r="C21" s="14" t="n">
         <v>46505</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="14" t="n">
         <v>46513</v>
       </c>
     </row>
@@ -5134,28 +5279,28 @@
           <t>Encerramento Contábil</t>
         </is>
       </c>
-      <c r="C22" s="11" t="n">
+      <c r="C22" s="14" t="n">
         <v>46514</v>
       </c>
-      <c r="D22" s="11" t="n">
+      <c r="D22" s="14" t="n">
         <v>46518</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>BLOCO 3 - 89267 - LD Xambioá II - Araguanã - 2XB2 - Instalação de 2 RT 34,5 kV</t>
         </is>
       </c>
-      <c r="C23" s="10" t="n">
+      <c r="C23" s="13" t="n">
         <v>46462</v>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D23" s="13" t="n">
         <v>46546</v>
       </c>
     </row>
@@ -5170,10 +5315,10 @@
           <t>Executar Obras</t>
         </is>
       </c>
-      <c r="C24" s="11" t="n">
+      <c r="C24" s="14" t="n">
         <v>46462</v>
       </c>
-      <c r="D24" s="11" t="n">
+      <c r="D24" s="14" t="n">
         <v>46492</v>
       </c>
     </row>
@@ -5188,10 +5333,10 @@
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C25" s="11" t="n">
+      <c r="C25" s="14" t="n">
         <v>46492</v>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D25" s="14" t="n">
         <v>46492</v>
       </c>
     </row>
@@ -5206,10 +5351,10 @@
           <t>Fiscalização</t>
         </is>
       </c>
-      <c r="C26" s="11" t="n">
+      <c r="C26" s="14" t="n">
         <v>46493</v>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="D26" s="14" t="n">
         <v>46505</v>
       </c>
     </row>
@@ -5224,10 +5369,10 @@
           <t>Cadastro EO / Integração parcial</t>
         </is>
       </c>
-      <c r="C27" s="11" t="n">
+      <c r="C27" s="14" t="n">
         <v>46506</v>
       </c>
-      <c r="D27" s="11" t="n">
+      <c r="D27" s="14" t="n">
         <v>46516</v>
       </c>
     </row>
@@ -5242,10 +5387,10 @@
           <t>Entrega do TCI pela empreiteira / Integração final</t>
         </is>
       </c>
-      <c r="C28" s="11" t="n">
+      <c r="C28" s="14" t="n">
         <v>46517</v>
       </c>
-      <c r="D28" s="11" t="n">
+      <c r="D28" s="14" t="n">
         <v>46532</v>
       </c>
     </row>
@@ -5260,10 +5405,10 @@
           <t>Comissionar Equipamentos</t>
         </is>
       </c>
-      <c r="C29" s="11" t="n">
+      <c r="C29" s="14" t="n">
         <v>46517</v>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D29" s="14" t="n">
         <v>46532</v>
       </c>
     </row>
@@ -5278,10 +5423,10 @@
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C30" s="11" t="n">
+      <c r="C30" s="14" t="n">
         <v>46532</v>
       </c>
-      <c r="D30" s="11" t="n">
+      <c r="D30" s="14" t="n">
         <v>46532</v>
       </c>
     </row>
@@ -5296,10 +5441,10 @@
           <t>Encerramento Técnico</t>
         </is>
       </c>
-      <c r="C31" s="11" t="n">
+      <c r="C31" s="14" t="n">
         <v>46533</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D31" s="14" t="n">
         <v>46541</v>
       </c>
     </row>
@@ -5314,28 +5459,28 @@
           <t>Encerramento Contábil</t>
         </is>
       </c>
-      <c r="C32" s="11" t="n">
+      <c r="C32" s="14" t="n">
         <v>46542</v>
       </c>
-      <c r="D32" s="11" t="n">
+      <c r="D32" s="14" t="n">
         <v>46546</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>BLOCO 4 - 91979 - QS-LD Gurupi - Duere - Instalação de 1 RL rural 34,5 kV + 3 TripSaver</t>
         </is>
       </c>
-      <c r="C33" s="10" t="n">
+      <c r="C33" s="13" t="n">
         <v>46462</v>
       </c>
-      <c r="D33" s="10" t="n">
+      <c r="D33" s="13" t="n">
         <v>46546</v>
       </c>
     </row>
@@ -5350,10 +5495,10 @@
           <t>Executar Obras</t>
         </is>
       </c>
-      <c r="C34" s="11" t="n">
+      <c r="C34" s="14" t="n">
         <v>46462</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="D34" s="14" t="n">
         <v>46492</v>
       </c>
     </row>
@@ -5368,10 +5513,10 @@
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C35" s="11" t="n">
+      <c r="C35" s="14" t="n">
         <v>46492</v>
       </c>
-      <c r="D35" s="11" t="n">
+      <c r="D35" s="14" t="n">
         <v>46492</v>
       </c>
     </row>
@@ -5386,10 +5531,10 @@
           <t>Fiscalização</t>
         </is>
       </c>
-      <c r="C36" s="11" t="n">
+      <c r="C36" s="14" t="n">
         <v>46493</v>
       </c>
-      <c r="D36" s="11" t="n">
+      <c r="D36" s="14" t="n">
         <v>46505</v>
       </c>
     </row>
@@ -5404,10 +5549,10 @@
           <t>Cadastro EO / Integração parcial</t>
         </is>
       </c>
-      <c r="C37" s="11" t="n">
+      <c r="C37" s="14" t="n">
         <v>46506</v>
       </c>
-      <c r="D37" s="11" t="n">
+      <c r="D37" s="14" t="n">
         <v>46516</v>
       </c>
     </row>
@@ -5422,10 +5567,10 @@
           <t>Entrega do TCI pela empreiteira / Integração final</t>
         </is>
       </c>
-      <c r="C38" s="11" t="n">
+      <c r="C38" s="14" t="n">
         <v>46517</v>
       </c>
-      <c r="D38" s="11" t="n">
+      <c r="D38" s="14" t="n">
         <v>46532</v>
       </c>
     </row>
@@ -5440,10 +5585,10 @@
           <t>Abertura de chamado / Atendimento GAT</t>
         </is>
       </c>
-      <c r="C39" s="11" t="n">
+      <c r="C39" s="14" t="n">
         <v>46517</v>
       </c>
-      <c r="D39" s="11" t="n">
+      <c r="D39" s="14" t="n">
         <v>46525</v>
       </c>
     </row>
@@ -5458,10 +5603,10 @@
           <t>Comissionar Equipamentos</t>
         </is>
       </c>
-      <c r="C40" s="11" t="n">
+      <c r="C40" s="14" t="n">
         <v>46517</v>
       </c>
-      <c r="D40" s="11" t="n">
+      <c r="D40" s="14" t="n">
         <v>46532</v>
       </c>
     </row>
@@ -5476,10 +5621,10 @@
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C41" s="11" t="n">
+      <c r="C41" s="14" t="n">
         <v>46532</v>
       </c>
-      <c r="D41" s="11" t="n">
+      <c r="D41" s="14" t="n">
         <v>46532</v>
       </c>
     </row>
@@ -5494,10 +5639,10 @@
           <t>Encerramento Técnico</t>
         </is>
       </c>
-      <c r="C42" s="11" t="n">
+      <c r="C42" s="14" t="n">
         <v>46533</v>
       </c>
-      <c r="D42" s="11" t="n">
+      <c r="D42" s="14" t="n">
         <v>46541</v>
       </c>
     </row>
@@ -5512,28 +5657,28 @@
           <t>Encerramento Contábil</t>
         </is>
       </c>
-      <c r="C43" s="11" t="n">
+      <c r="C43" s="14" t="n">
         <v>46542</v>
       </c>
-      <c r="D43" s="11" t="n">
+      <c r="D43" s="14" t="n">
         <v>46546</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>BLOCO 5 - 92118 - QS-4 de Araguaína IV - Instalação de 1 RL 13,8 kV</t>
         </is>
       </c>
-      <c r="C44" s="10" t="n">
+      <c r="C44" s="13" t="n">
         <v>46462</v>
       </c>
-      <c r="D44" s="10" t="n">
+      <c r="D44" s="13" t="n">
         <v>46546</v>
       </c>
     </row>
@@ -5548,10 +5693,10 @@
           <t>Executar Obras</t>
         </is>
       </c>
-      <c r="C45" s="11" t="n">
+      <c r="C45" s="14" t="n">
         <v>46462</v>
       </c>
-      <c r="D45" s="11" t="n">
+      <c r="D45" s="14" t="n">
         <v>46492</v>
       </c>
     </row>
@@ -5566,10 +5711,10 @@
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C46" s="11" t="n">
+      <c r="C46" s="14" t="n">
         <v>46492</v>
       </c>
-      <c r="D46" s="11" t="n">
+      <c r="D46" s="14" t="n">
         <v>46492</v>
       </c>
     </row>
@@ -5584,10 +5729,10 @@
           <t>Fiscalização</t>
         </is>
       </c>
-      <c r="C47" s="11" t="n">
+      <c r="C47" s="14" t="n">
         <v>46493</v>
       </c>
-      <c r="D47" s="11" t="n">
+      <c r="D47" s="14" t="n">
         <v>46505</v>
       </c>
     </row>
@@ -5602,10 +5747,10 @@
           <t>Cadastro EO / Integração parcial</t>
         </is>
       </c>
-      <c r="C48" s="11" t="n">
+      <c r="C48" s="14" t="n">
         <v>46506</v>
       </c>
-      <c r="D48" s="11" t="n">
+      <c r="D48" s="14" t="n">
         <v>46516</v>
       </c>
     </row>
@@ -5620,10 +5765,10 @@
           <t>Entrega do TCI pela empreiteira / Integração final</t>
         </is>
       </c>
-      <c r="C49" s="11" t="n">
+      <c r="C49" s="14" t="n">
         <v>46517</v>
       </c>
-      <c r="D49" s="11" t="n">
+      <c r="D49" s="14" t="n">
         <v>46532</v>
       </c>
     </row>
@@ -5638,10 +5783,10 @@
           <t>Abertura de chamado / Atendimento GAT</t>
         </is>
       </c>
-      <c r="C50" s="11" t="n">
+      <c r="C50" s="14" t="n">
         <v>46517</v>
       </c>
-      <c r="D50" s="11" t="n">
+      <c r="D50" s="14" t="n">
         <v>46525</v>
       </c>
     </row>
@@ -5656,10 +5801,10 @@
           <t>Comissionar Equipamentos</t>
         </is>
       </c>
-      <c r="C51" s="11" t="n">
+      <c r="C51" s="14" t="n">
         <v>46517</v>
       </c>
-      <c r="D51" s="11" t="n">
+      <c r="D51" s="14" t="n">
         <v>46532</v>
       </c>
     </row>
@@ -5674,10 +5819,10 @@
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C52" s="11" t="n">
+      <c r="C52" s="14" t="n">
         <v>46532</v>
       </c>
-      <c r="D52" s="11" t="n">
+      <c r="D52" s="14" t="n">
         <v>46532</v>
       </c>
     </row>
@@ -5692,10 +5837,10 @@
           <t>Encerramento Técnico</t>
         </is>
       </c>
-      <c r="C53" s="11" t="n">
+      <c r="C53" s="14" t="n">
         <v>46533</v>
       </c>
-      <c r="D53" s="11" t="n">
+      <c r="D53" s="14" t="n">
         <v>46541</v>
       </c>
     </row>
@@ -5710,28 +5855,28 @@
           <t>Encerramento Contábil</t>
         </is>
       </c>
-      <c r="C54" s="11" t="n">
+      <c r="C54" s="14" t="n">
         <v>46542</v>
       </c>
-      <c r="D54" s="11" t="n">
+      <c r="D54" s="14" t="n">
         <v>46546</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>BLOCO 6 - 70838 - LD Cristalândia - Lagoa da Confusão - Instalação de 1 RT 34,5 kV</t>
         </is>
       </c>
-      <c r="C55" s="10" t="n">
+      <c r="C55" s="13" t="n">
         <v>46497</v>
       </c>
-      <c r="D55" s="10" t="n">
+      <c r="D55" s="13" t="n">
         <v>46581</v>
       </c>
     </row>
@@ -5746,10 +5891,10 @@
           <t>Executar Obras</t>
         </is>
       </c>
-      <c r="C56" s="11" t="n">
+      <c r="C56" s="14" t="n">
         <v>46497</v>
       </c>
-      <c r="D56" s="11" t="n">
+      <c r="D56" s="14" t="n">
         <v>46527</v>
       </c>
     </row>
@@ -5764,10 +5909,10 @@
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C57" s="11" t="n">
+      <c r="C57" s="14" t="n">
         <v>46527</v>
       </c>
-      <c r="D57" s="11" t="n">
+      <c r="D57" s="14" t="n">
         <v>46527</v>
       </c>
     </row>
@@ -5782,10 +5927,10 @@
           <t>Fiscalização</t>
         </is>
       </c>
-      <c r="C58" s="11" t="n">
+      <c r="C58" s="14" t="n">
         <v>46528</v>
       </c>
-      <c r="D58" s="11" t="n">
+      <c r="D58" s="14" t="n">
         <v>46540</v>
       </c>
     </row>
@@ -5800,10 +5945,10 @@
           <t>Cadastro EO / Integração parcial</t>
         </is>
       </c>
-      <c r="C59" s="11" t="n">
+      <c r="C59" s="14" t="n">
         <v>46541</v>
       </c>
-      <c r="D59" s="11" t="n">
+      <c r="D59" s="14" t="n">
         <v>46551</v>
       </c>
     </row>
@@ -5818,10 +5963,10 @@
           <t>Entrega do TCI pela empreiteira / Integração final</t>
         </is>
       </c>
-      <c r="C60" s="11" t="n">
+      <c r="C60" s="14" t="n">
         <v>46552</v>
       </c>
-      <c r="D60" s="11" t="n">
+      <c r="D60" s="14" t="n">
         <v>46567</v>
       </c>
     </row>
@@ -5836,10 +5981,10 @@
           <t>Comissionar Equipamentos</t>
         </is>
       </c>
-      <c r="C61" s="11" t="n">
+      <c r="C61" s="14" t="n">
         <v>46552</v>
       </c>
-      <c r="D61" s="11" t="n">
+      <c r="D61" s="14" t="n">
         <v>46567</v>
       </c>
     </row>
@@ -5854,10 +5999,10 @@
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C62" s="11" t="n">
+      <c r="C62" s="14" t="n">
         <v>46567</v>
       </c>
-      <c r="D62" s="11" t="n">
+      <c r="D62" s="14" t="n">
         <v>46567</v>
       </c>
     </row>
@@ -5872,10 +6017,10 @@
           <t>Encerramento Técnico</t>
         </is>
       </c>
-      <c r="C63" s="11" t="n">
+      <c r="C63" s="14" t="n">
         <v>46568</v>
       </c>
-      <c r="D63" s="11" t="n">
+      <c r="D63" s="14" t="n">
         <v>46576</v>
       </c>
     </row>
@@ -5890,28 +6035,28 @@
           <t>Encerramento Contábil</t>
         </is>
       </c>
-      <c r="C64" s="11" t="n">
+      <c r="C64" s="14" t="n">
         <v>46577</v>
       </c>
-      <c r="D64" s="11" t="n">
+      <c r="D64" s="14" t="n">
         <v>46581</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>BLOCO 7 - 70978 - LD Paraíso I - Caseara - 2PR0 - Instalação de 1 RT 34,5 kV</t>
         </is>
       </c>
-      <c r="C65" s="10" t="n">
+      <c r="C65" s="13" t="n">
         <v>46497</v>
       </c>
-      <c r="D65" s="10" t="n">
+      <c r="D65" s="13" t="n">
         <v>46581</v>
       </c>
     </row>
@@ -5926,10 +6071,10 @@
           <t>Executar Obras</t>
         </is>
       </c>
-      <c r="C66" s="11" t="n">
+      <c r="C66" s="14" t="n">
         <v>46497</v>
       </c>
-      <c r="D66" s="11" t="n">
+      <c r="D66" s="14" t="n">
         <v>46527</v>
       </c>
     </row>
@@ -5944,10 +6089,10 @@
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C67" s="11" t="n">
+      <c r="C67" s="14" t="n">
         <v>46527</v>
       </c>
-      <c r="D67" s="11" t="n">
+      <c r="D67" s="14" t="n">
         <v>46527</v>
       </c>
     </row>
@@ -5962,10 +6107,10 @@
           <t>Fiscalização</t>
         </is>
       </c>
-      <c r="C68" s="11" t="n">
+      <c r="C68" s="14" t="n">
         <v>46528</v>
       </c>
-      <c r="D68" s="11" t="n">
+      <c r="D68" s="14" t="n">
         <v>46540</v>
       </c>
     </row>
@@ -5980,10 +6125,10 @@
           <t>Cadastro EO / Integração parcial</t>
         </is>
       </c>
-      <c r="C69" s="11" t="n">
+      <c r="C69" s="14" t="n">
         <v>46541</v>
       </c>
-      <c r="D69" s="11" t="n">
+      <c r="D69" s="14" t="n">
         <v>46551</v>
       </c>
     </row>
@@ -5998,10 +6143,10 @@
           <t>Entrega do TCI pela empreiteira / Integração final</t>
         </is>
       </c>
-      <c r="C70" s="11" t="n">
+      <c r="C70" s="14" t="n">
         <v>46552</v>
       </c>
-      <c r="D70" s="11" t="n">
+      <c r="D70" s="14" t="n">
         <v>46567</v>
       </c>
     </row>
@@ -6016,10 +6161,10 @@
           <t>Comissionar Equipamentos</t>
         </is>
       </c>
-      <c r="C71" s="11" t="n">
+      <c r="C71" s="14" t="n">
         <v>46552</v>
       </c>
-      <c r="D71" s="11" t="n">
+      <c r="D71" s="14" t="n">
         <v>46567</v>
       </c>
     </row>
@@ -6034,10 +6179,10 @@
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C72" s="11" t="n">
+      <c r="C72" s="14" t="n">
         <v>46567</v>
       </c>
-      <c r="D72" s="11" t="n">
+      <c r="D72" s="14" t="n">
         <v>46567</v>
       </c>
     </row>
@@ -6052,10 +6197,10 @@
           <t>Encerramento Técnico</t>
         </is>
       </c>
-      <c r="C73" s="11" t="n">
+      <c r="C73" s="14" t="n">
         <v>46568</v>
       </c>
-      <c r="D73" s="11" t="n">
+      <c r="D73" s="14" t="n">
         <v>46576</v>
       </c>
     </row>
@@ -6070,28 +6215,28 @@
           <t>Encerramento Contábil</t>
         </is>
       </c>
-      <c r="C74" s="11" t="n">
+      <c r="C74" s="14" t="n">
         <v>46577</v>
       </c>
-      <c r="D74" s="11" t="n">
+      <c r="D74" s="14" t="n">
         <v>46581</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>BLOCO 8 - 92094 - QS-LD Palmas - Aparecida do Rio Negro - Instalação de 3 RL 34,5 kV</t>
         </is>
       </c>
-      <c r="C75" s="10" t="n">
+      <c r="C75" s="13" t="n">
         <v>46497</v>
       </c>
-      <c r="D75" s="10" t="n">
+      <c r="D75" s="13" t="n">
         <v>46581</v>
       </c>
     </row>
@@ -6106,10 +6251,10 @@
           <t>Executar Obras</t>
         </is>
       </c>
-      <c r="C76" s="11" t="n">
+      <c r="C76" s="14" t="n">
         <v>46497</v>
       </c>
-      <c r="D76" s="11" t="n">
+      <c r="D76" s="14" t="n">
         <v>46527</v>
       </c>
     </row>
@@ -6124,10 +6269,10 @@
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C77" s="11" t="n">
+      <c r="C77" s="14" t="n">
         <v>46527</v>
       </c>
-      <c r="D77" s="11" t="n">
+      <c r="D77" s="14" t="n">
         <v>46527</v>
       </c>
     </row>
@@ -6142,10 +6287,10 @@
           <t>Fiscalização</t>
         </is>
       </c>
-      <c r="C78" s="11" t="n">
+      <c r="C78" s="14" t="n">
         <v>46528</v>
       </c>
-      <c r="D78" s="11" t="n">
+      <c r="D78" s="14" t="n">
         <v>46540</v>
       </c>
     </row>
@@ -6160,10 +6305,10 @@
           <t>Cadastro EO / Integração parcial</t>
         </is>
       </c>
-      <c r="C79" s="11" t="n">
+      <c r="C79" s="14" t="n">
         <v>46541</v>
       </c>
-      <c r="D79" s="11" t="n">
+      <c r="D79" s="14" t="n">
         <v>46551</v>
       </c>
     </row>
@@ -6178,10 +6323,10 @@
           <t>Entrega do TCI pela empreiteira / Integração final</t>
         </is>
       </c>
-      <c r="C80" s="11" t="n">
+      <c r="C80" s="14" t="n">
         <v>46552</v>
       </c>
-      <c r="D80" s="11" t="n">
+      <c r="D80" s="14" t="n">
         <v>46567</v>
       </c>
     </row>
@@ -6196,10 +6341,10 @@
           <t>Abertura de chamado / Atendimento GAT</t>
         </is>
       </c>
-      <c r="C81" s="11" t="n">
+      <c r="C81" s="14" t="n">
         <v>46552</v>
       </c>
-      <c r="D81" s="11" t="n">
+      <c r="D81" s="14" t="n">
         <v>46560</v>
       </c>
     </row>
@@ -6214,10 +6359,10 @@
           <t>Comissionar Equipamentos</t>
         </is>
       </c>
-      <c r="C82" s="11" t="n">
+      <c r="C82" s="14" t="n">
         <v>46552</v>
       </c>
-      <c r="D82" s="11" t="n">
+      <c r="D82" s="14" t="n">
         <v>46567</v>
       </c>
     </row>
@@ -6232,10 +6377,10 @@
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C83" s="11" t="n">
+      <c r="C83" s="14" t="n">
         <v>46567</v>
       </c>
-      <c r="D83" s="11" t="n">
+      <c r="D83" s="14" t="n">
         <v>46567</v>
       </c>
     </row>
@@ -6250,10 +6395,10 @@
           <t>Encerramento Técnico</t>
         </is>
       </c>
-      <c r="C84" s="11" t="n">
+      <c r="C84" s="14" t="n">
         <v>46568</v>
       </c>
-      <c r="D84" s="11" t="n">
+      <c r="D84" s="14" t="n">
         <v>46576</v>
       </c>
     </row>
@@ -6268,28 +6413,28 @@
           <t>Encerramento Contábil</t>
         </is>
       </c>
-      <c r="C85" s="11" t="n">
+      <c r="C85" s="14" t="n">
         <v>46577</v>
       </c>
-      <c r="D85" s="11" t="n">
+      <c r="D85" s="14" t="n">
         <v>46581</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>BLOCO 9 - 92095 - QS-LD Palmas - Lajeado - Instalação de 1 RL 34,5 kV</t>
         </is>
       </c>
-      <c r="C86" s="10" t="n">
+      <c r="C86" s="13" t="n">
         <v>46497</v>
       </c>
-      <c r="D86" s="10" t="n">
+      <c r="D86" s="13" t="n">
         <v>46581</v>
       </c>
     </row>
@@ -6304,10 +6449,10 @@
           <t>Executar Obras</t>
         </is>
       </c>
-      <c r="C87" s="11" t="n">
+      <c r="C87" s="14" t="n">
         <v>46497</v>
       </c>
-      <c r="D87" s="11" t="n">
+      <c r="D87" s="14" t="n">
         <v>46527</v>
       </c>
     </row>
@@ -6322,10 +6467,10 @@
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C88" s="11" t="n">
+      <c r="C88" s="14" t="n">
         <v>46527</v>
       </c>
-      <c r="D88" s="11" t="n">
+      <c r="D88" s="14" t="n">
         <v>46527</v>
       </c>
     </row>
@@ -6340,10 +6485,10 @@
           <t>Fiscalização</t>
         </is>
       </c>
-      <c r="C89" s="11" t="n">
+      <c r="C89" s="14" t="n">
         <v>46528</v>
       </c>
-      <c r="D89" s="11" t="n">
+      <c r="D89" s="14" t="n">
         <v>46540</v>
       </c>
     </row>
@@ -6358,10 +6503,10 @@
           <t>Cadastro EO / Integração parcial</t>
         </is>
       </c>
-      <c r="C90" s="11" t="n">
+      <c r="C90" s="14" t="n">
         <v>46541</v>
       </c>
-      <c r="D90" s="11" t="n">
+      <c r="D90" s="14" t="n">
         <v>46551</v>
       </c>
     </row>
@@ -6376,10 +6521,10 @@
           <t>Entrega do TCI pela empreiteira / Integração final</t>
         </is>
       </c>
-      <c r="C91" s="11" t="n">
+      <c r="C91" s="14" t="n">
         <v>46552</v>
       </c>
-      <c r="D91" s="11" t="n">
+      <c r="D91" s="14" t="n">
         <v>46567</v>
       </c>
     </row>
@@ -6394,10 +6539,10 @@
           <t>Abertura de chamado / Atendimento GAT</t>
         </is>
       </c>
-      <c r="C92" s="11" t="n">
+      <c r="C92" s="14" t="n">
         <v>46552</v>
       </c>
-      <c r="D92" s="11" t="n">
+      <c r="D92" s="14" t="n">
         <v>46560</v>
       </c>
     </row>
@@ -6412,10 +6557,10 @@
           <t>Comissionar Equipamentos</t>
         </is>
       </c>
-      <c r="C93" s="11" t="n">
+      <c r="C93" s="14" t="n">
         <v>46552</v>
       </c>
-      <c r="D93" s="11" t="n">
+      <c r="D93" s="14" t="n">
         <v>46567</v>
       </c>
     </row>
@@ -6430,10 +6575,10 @@
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C94" s="11" t="n">
+      <c r="C94" s="14" t="n">
         <v>46567</v>
       </c>
-      <c r="D94" s="11" t="n">
+      <c r="D94" s="14" t="n">
         <v>46567</v>
       </c>
     </row>
@@ -6448,10 +6593,10 @@
           <t>Encerramento Técnico</t>
         </is>
       </c>
-      <c r="C95" s="11" t="n">
+      <c r="C95" s="14" t="n">
         <v>46568</v>
       </c>
-      <c r="D95" s="11" t="n">
+      <c r="D95" s="14" t="n">
         <v>46576</v>
       </c>
     </row>
@@ -6466,28 +6611,28 @@
           <t>Encerramento Contábil</t>
         </is>
       </c>
-      <c r="C96" s="11" t="n">
+      <c r="C96" s="14" t="n">
         <v>46577</v>
       </c>
-      <c r="D96" s="11" t="n">
+      <c r="D96" s="14" t="n">
         <v>46581</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>1.10</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>BLOCO 10 - 92101 - QS-8 de Palmas IV - Instalação de 1 RL 13,8 kV</t>
         </is>
       </c>
-      <c r="C97" s="10" t="n">
+      <c r="C97" s="13" t="n">
         <v>46497</v>
       </c>
-      <c r="D97" s="10" t="n">
+      <c r="D97" s="13" t="n">
         <v>46581</v>
       </c>
     </row>
@@ -6502,10 +6647,10 @@
           <t>Executar Obras</t>
         </is>
       </c>
-      <c r="C98" s="11" t="n">
+      <c r="C98" s="14" t="n">
         <v>46497</v>
       </c>
-      <c r="D98" s="11" t="n">
+      <c r="D98" s="14" t="n">
         <v>46527</v>
       </c>
     </row>
@@ -6520,10 +6665,10 @@
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C99" s="11" t="n">
+      <c r="C99" s="14" t="n">
         <v>46527</v>
       </c>
-      <c r="D99" s="11" t="n">
+      <c r="D99" s="14" t="n">
         <v>46527</v>
       </c>
     </row>
@@ -6538,10 +6683,10 @@
           <t>Fiscalização</t>
         </is>
       </c>
-      <c r="C100" s="11" t="n">
+      <c r="C100" s="14" t="n">
         <v>46528</v>
       </c>
-      <c r="D100" s="11" t="n">
+      <c r="D100" s="14" t="n">
         <v>46540</v>
       </c>
     </row>
@@ -6556,10 +6701,10 @@
           <t>Cadastro EO / Integração parcial</t>
         </is>
       </c>
-      <c r="C101" s="11" t="n">
+      <c r="C101" s="14" t="n">
         <v>46541</v>
       </c>
-      <c r="D101" s="11" t="n">
+      <c r="D101" s="14" t="n">
         <v>46551</v>
       </c>
     </row>
@@ -6574,10 +6719,10 @@
           <t>Entrega do TCI pela empreiteira / Integração final</t>
         </is>
       </c>
-      <c r="C102" s="11" t="n">
+      <c r="C102" s="14" t="n">
         <v>46552</v>
       </c>
-      <c r="D102" s="11" t="n">
+      <c r="D102" s="14" t="n">
         <v>46567</v>
       </c>
     </row>
@@ -6592,10 +6737,10 @@
           <t>Abertura de chamado / Atendimento GAT</t>
         </is>
       </c>
-      <c r="C103" s="11" t="n">
+      <c r="C103" s="14" t="n">
         <v>46552</v>
       </c>
-      <c r="D103" s="11" t="n">
+      <c r="D103" s="14" t="n">
         <v>46560</v>
       </c>
     </row>
@@ -6610,10 +6755,10 @@
           <t>Comissionar Equipamentos</t>
         </is>
       </c>
-      <c r="C104" s="11" t="n">
+      <c r="C104" s="14" t="n">
         <v>46552</v>
       </c>
-      <c r="D104" s="11" t="n">
+      <c r="D104" s="14" t="n">
         <v>46567</v>
       </c>
     </row>
@@ -6628,10 +6773,10 @@
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C105" s="11" t="n">
+      <c r="C105" s="14" t="n">
         <v>46567</v>
       </c>
-      <c r="D105" s="11" t="n">
+      <c r="D105" s="14" t="n">
         <v>46567</v>
       </c>
     </row>
@@ -6646,10 +6791,10 @@
           <t>Encerramento Técnico</t>
         </is>
       </c>
-      <c r="C106" s="11" t="n">
+      <c r="C106" s="14" t="n">
         <v>46568</v>
       </c>
-      <c r="D106" s="11" t="n">
+      <c r="D106" s="14" t="n">
         <v>46576</v>
       </c>
     </row>
@@ -6664,28 +6809,28 @@
           <t>Encerramento Contábil</t>
         </is>
       </c>
-      <c r="C107" s="11" t="n">
+      <c r="C107" s="14" t="n">
         <v>46577</v>
       </c>
-      <c r="D107" s="11" t="n">
+      <c r="D107" s="14" t="n">
         <v>46581</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>1.11</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>BLOCO 11 - 92102 - QS-6 de Palmas IV - Instalação de 1 RL 13,8 kV</t>
         </is>
       </c>
-      <c r="C108" s="10" t="n">
+      <c r="C108" s="13" t="n">
         <v>46497</v>
       </c>
-      <c r="D108" s="10" t="n">
+      <c r="D108" s="13" t="n">
         <v>46581</v>
       </c>
     </row>
@@ -6700,10 +6845,10 @@
           <t>Executar Obras</t>
         </is>
       </c>
-      <c r="C109" s="11" t="n">
+      <c r="C109" s="14" t="n">
         <v>46497</v>
       </c>
-      <c r="D109" s="11" t="n">
+      <c r="D109" s="14" t="n">
         <v>46527</v>
       </c>
     </row>
@@ -6718,10 +6863,10 @@
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C110" s="11" t="n">
+      <c r="C110" s="14" t="n">
         <v>46527</v>
       </c>
-      <c r="D110" s="11" t="n">
+      <c r="D110" s="14" t="n">
         <v>46527</v>
       </c>
     </row>
@@ -6736,10 +6881,10 @@
           <t>Fiscalização</t>
         </is>
       </c>
-      <c r="C111" s="11" t="n">
+      <c r="C111" s="14" t="n">
         <v>46528</v>
       </c>
-      <c r="D111" s="11" t="n">
+      <c r="D111" s="14" t="n">
         <v>46540</v>
       </c>
     </row>
@@ -6754,10 +6899,10 @@
           <t>Cadastro EO / Integração parcial</t>
         </is>
       </c>
-      <c r="C112" s="11" t="n">
+      <c r="C112" s="14" t="n">
         <v>46541</v>
       </c>
-      <c r="D112" s="11" t="n">
+      <c r="D112" s="14" t="n">
         <v>46551</v>
       </c>
     </row>
@@ -6772,10 +6917,10 @@
           <t>Entrega do TCI pela empreiteira / Integração final</t>
         </is>
       </c>
-      <c r="C113" s="11" t="n">
+      <c r="C113" s="14" t="n">
         <v>46552</v>
       </c>
-      <c r="D113" s="11" t="n">
+      <c r="D113" s="14" t="n">
         <v>46567</v>
       </c>
     </row>
@@ -6790,10 +6935,10 @@
           <t>Abertura de chamado / Atendimento GAT</t>
         </is>
       </c>
-      <c r="C114" s="11" t="n">
+      <c r="C114" s="14" t="n">
         <v>46552</v>
       </c>
-      <c r="D114" s="11" t="n">
+      <c r="D114" s="14" t="n">
         <v>46560</v>
       </c>
     </row>
@@ -6808,10 +6953,10 @@
           <t>Comissionar Equipamentos</t>
         </is>
       </c>
-      <c r="C115" s="11" t="n">
+      <c r="C115" s="14" t="n">
         <v>46552</v>
       </c>
-      <c r="D115" s="11" t="n">
+      <c r="D115" s="14" t="n">
         <v>46567</v>
       </c>
     </row>
@@ -6826,10 +6971,10 @@
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C116" s="11" t="n">
+      <c r="C116" s="14" t="n">
         <v>46567</v>
       </c>
-      <c r="D116" s="11" t="n">
+      <c r="D116" s="14" t="n">
         <v>46567</v>
       </c>
     </row>
@@ -6844,10 +6989,10 @@
           <t>Encerramento Técnico</t>
         </is>
       </c>
-      <c r="C117" s="11" t="n">
+      <c r="C117" s="14" t="n">
         <v>46568</v>
       </c>
-      <c r="D117" s="11" t="n">
+      <c r="D117" s="14" t="n">
         <v>46576</v>
       </c>
     </row>
@@ -6862,28 +7007,28 @@
           <t>Encerramento Contábil</t>
         </is>
       </c>
-      <c r="C118" s="11" t="n">
+      <c r="C118" s="14" t="n">
         <v>46577</v>
       </c>
-      <c r="D118" s="11" t="n">
+      <c r="D118" s="14" t="n">
         <v>46581</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="A119" s="6" t="inlineStr">
         <is>
           <t>1.12</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B119" s="6" t="inlineStr">
         <is>
           <t>BLOCO 12 - 89249 - LD Araguaína - Babaçulândia - 2AR0 - Instalação de 1 RT 34,5 kV</t>
         </is>
       </c>
-      <c r="C119" s="10" t="n">
+      <c r="C119" s="13" t="n">
         <v>46560</v>
       </c>
-      <c r="D119" s="10" t="n">
+      <c r="D119" s="13" t="n">
         <v>46644</v>
       </c>
     </row>
@@ -6898,10 +7043,10 @@
           <t>Executar Obras</t>
         </is>
       </c>
-      <c r="C120" s="11" t="n">
+      <c r="C120" s="14" t="n">
         <v>46560</v>
       </c>
-      <c r="D120" s="11" t="n">
+      <c r="D120" s="14" t="n">
         <v>46590</v>
       </c>
     </row>
@@ -6916,10 +7061,10 @@
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C121" s="11" t="n">
+      <c r="C121" s="14" t="n">
         <v>46590</v>
       </c>
-      <c r="D121" s="11" t="n">
+      <c r="D121" s="14" t="n">
         <v>46590</v>
       </c>
     </row>
@@ -6934,10 +7079,10 @@
           <t>Fiscalização</t>
         </is>
       </c>
-      <c r="C122" s="11" t="n">
+      <c r="C122" s="14" t="n">
         <v>46591</v>
       </c>
-      <c r="D122" s="11" t="n">
+      <c r="D122" s="14" t="n">
         <v>46603</v>
       </c>
     </row>
@@ -6952,10 +7097,10 @@
           <t>Cadastro EO / Integração parcial</t>
         </is>
       </c>
-      <c r="C123" s="11" t="n">
+      <c r="C123" s="14" t="n">
         <v>46604</v>
       </c>
-      <c r="D123" s="11" t="n">
+      <c r="D123" s="14" t="n">
         <v>46614</v>
       </c>
     </row>
@@ -6970,10 +7115,10 @@
           <t>Entrega do TCI pela empreiteira / Integração final</t>
         </is>
       </c>
-      <c r="C124" s="11" t="n">
+      <c r="C124" s="14" t="n">
         <v>46615</v>
       </c>
-      <c r="D124" s="11" t="n">
+      <c r="D124" s="14" t="n">
         <v>46630</v>
       </c>
     </row>
@@ -6988,10 +7133,10 @@
           <t>Comissionar Equipamentos</t>
         </is>
       </c>
-      <c r="C125" s="11" t="n">
+      <c r="C125" s="14" t="n">
         <v>46615</v>
       </c>
-      <c r="D125" s="11" t="n">
+      <c r="D125" s="14" t="n">
         <v>46630</v>
       </c>
     </row>
@@ -7006,10 +7151,10 @@
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C126" s="11" t="n">
+      <c r="C126" s="14" t="n">
         <v>46630</v>
       </c>
-      <c r="D126" s="11" t="n">
+      <c r="D126" s="14" t="n">
         <v>46630</v>
       </c>
     </row>
@@ -7024,10 +7169,10 @@
           <t>Encerramento Técnico</t>
         </is>
       </c>
-      <c r="C127" s="11" t="n">
+      <c r="C127" s="14" t="n">
         <v>46631</v>
       </c>
-      <c r="D127" s="11" t="n">
+      <c r="D127" s="14" t="n">
         <v>46639</v>
       </c>
     </row>
@@ -7042,28 +7187,28 @@
           <t>Encerramento Contábil</t>
         </is>
       </c>
-      <c r="C128" s="11" t="n">
+      <c r="C128" s="14" t="n">
         <v>46640</v>
       </c>
-      <c r="D128" s="11" t="n">
+      <c r="D128" s="14" t="n">
         <v>46644</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="A129" s="6" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B129" s="6" t="inlineStr">
         <is>
           <t>BLOCO 13 - 89307 - 1 de Figueirópolis - 2FGR - Instalação de 1 RT 13,8 kV + remanejamento de 1 RL</t>
         </is>
       </c>
-      <c r="C129" s="10" t="n">
+      <c r="C129" s="13" t="n">
         <v>46560</v>
       </c>
-      <c r="D129" s="10" t="n">
+      <c r="D129" s="13" t="n">
         <v>46644</v>
       </c>
     </row>
@@ -7078,10 +7223,10 @@
           <t>Executar Obras</t>
         </is>
       </c>
-      <c r="C130" s="11" t="n">
+      <c r="C130" s="14" t="n">
         <v>46560</v>
       </c>
-      <c r="D130" s="11" t="n">
+      <c r="D130" s="14" t="n">
         <v>46590</v>
       </c>
     </row>
@@ -7096,10 +7241,10 @@
           <t>Obras Concluídas (marco)</t>
         </is>
       </c>
-      <c r="C131" s="11" t="n">
+      <c r="C131" s="14" t="n">
         <v>46590</v>
       </c>
-      <c r="D131" s="11" t="n">
+      <c r="D131" s="14" t="n">
         <v>46590</v>
       </c>
     </row>
@@ -7114,10 +7259,10 @@
           <t>Fiscalização</t>
         </is>
       </c>
-      <c r="C132" s="11" t="n">
+      <c r="C132" s="14" t="n">
         <v>46591</v>
       </c>
-      <c r="D132" s="11" t="n">
+      <c r="D132" s="14" t="n">
         <v>46603</v>
       </c>
     </row>
@@ -7132,10 +7277,10 @@
           <t>Cadastro EO / Integração parcial</t>
         </is>
       </c>
-      <c r="C133" s="11" t="n">
+      <c r="C133" s="14" t="n">
         <v>46604</v>
       </c>
-      <c r="D133" s="11" t="n">
+      <c r="D133" s="14" t="n">
         <v>46614</v>
       </c>
     </row>
@@ -7150,10 +7295,10 @@
           <t>Entrega do TCI pela empreiteira / Integração final</t>
         </is>
       </c>
-      <c r="C134" s="11" t="n">
+      <c r="C134" s="14" t="n">
         <v>46615</v>
       </c>
-      <c r="D134" s="11" t="n">
+      <c r="D134" s="14" t="n">
         <v>46630</v>
       </c>
     </row>
@@ -7168,10 +7313,10 @@
           <t>Abertura de chamado / Atendimento GAT</t>
         </is>
       </c>
-      <c r="C135" s="11" t="n">
+      <c r="C135" s="14" t="n">
         <v>46615</v>
       </c>
-      <c r="D135" s="11" t="n">
+      <c r="D135" s="14" t="n">
         <v>46623</v>
       </c>
     </row>
@@ -7186,10 +7331,10 @@
           <t>Comissionar Equipamentos</t>
         </is>
       </c>
-      <c r="C136" s="11" t="n">
+      <c r="C136" s="14" t="n">
         <v>46615</v>
       </c>
-      <c r="D136" s="11" t="n">
+      <c r="D136" s="14" t="n">
         <v>46630</v>
       </c>
     </row>
@@ -7204,10 +7349,10 @@
           <t>Equipamentos em Operação / Energização (marco)</t>
         </is>
       </c>
-      <c r="C137" s="11" t="n">
+      <c r="C137" s="14" t="n">
         <v>46630</v>
       </c>
-      <c r="D137" s="11" t="n">
+      <c r="D137" s="14" t="n">
         <v>46630</v>
       </c>
     </row>
@@ -7222,10 +7367,10 @@
           <t>Encerramento Técnico</t>
         </is>
       </c>
-      <c r="C138" s="11" t="n">
+      <c r="C138" s="14" t="n">
         <v>46631</v>
       </c>
-      <c r="D138" s="11" t="n">
+      <c r="D138" s="14" t="n">
         <v>46639</v>
       </c>
     </row>
@@ -7240,10 +7385,10 @@
           <t>Encerramento Contábil</t>
         </is>
       </c>
-      <c r="C139" s="11" t="n">
+      <c r="C139" s="14" t="n">
         <v>46640</v>
       </c>
-      <c r="D139" s="11" t="n">
+      <c r="D139" s="14" t="n">
         <v>46644</v>
       </c>
     </row>
@@ -7269,14 +7414,15 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -7300,97 +7446,97 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>SIGCO</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Projeto</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>Energização (PN)</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>Fev</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Abr</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>Mai</t>
         </is>
       </c>
-      <c r="J1" s="12" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="K1" s="12" t="inlineStr">
+      <c r="K1" s="15" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="L1" s="12" t="inlineStr">
+      <c r="L1" s="15" t="inlineStr">
         <is>
           <t>Ago</t>
         </is>
       </c>
-      <c r="M1" s="12" t="inlineStr">
+      <c r="M1" s="15" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N1" s="12" t="inlineStr">
+      <c r="N1" s="15" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="O1" s="12" t="inlineStr">
+      <c r="O1" s="15" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="P1" s="12" t="inlineStr">
+      <c r="P1" s="15" t="inlineStr">
         <is>
           <t>Dez</t>
         </is>
       </c>
-      <c r="Q1" s="12" t="inlineStr">
+      <c r="Q1" s="15" t="inlineStr">
         <is>
           <t>Total 2027 (R$)</t>
         </is>
       </c>
-      <c r="R1" s="12" t="inlineStr">
+      <c r="R1" s="15" t="inlineStr">
         <is>
           <t>Base ago/26 (R$)</t>
         </is>
       </c>
-      <c r="S1" s="12" t="inlineStr">
+      <c r="S1" s="15" t="inlineStr">
         <is>
           <t>Δ (R$)</t>
         </is>
@@ -7410,53 +7556,53 @@
           <t>QP</t>
         </is>
       </c>
-      <c r="D2" s="13" t="n">
+      <c r="D2" s="16" t="n">
         <v>46478</v>
       </c>
-      <c r="E2" s="14" t="n">
+      <c r="E2" s="3" t="n">
         <v>143320.11</v>
       </c>
-      <c r="F2" s="14" t="n">
+      <c r="F2" s="3" t="n">
         <v>143320.11</v>
       </c>
-      <c r="G2" s="14" t="n">
+      <c r="G2" s="3" t="n">
         <v>143320.11</v>
       </c>
-      <c r="H2" s="14" t="n">
+      <c r="H2" s="3" t="n">
         <v>143320.11</v>
       </c>
-      <c r="I2" s="14" t="n">
+      <c r="I2" s="3" t="n">
         <v>163760.56</v>
       </c>
-      <c r="J2" s="14" t="n">
+      <c r="J2" s="3" t="n">
         <v>163760.56</v>
       </c>
-      <c r="K2" s="14" t="n">
+      <c r="K2" s="3" t="n">
         <v>163760.56</v>
       </c>
-      <c r="L2" s="14" t="n">
+      <c r="L2" s="3" t="n">
         <v>163760.37</v>
       </c>
-      <c r="M2" s="14" t="n">
+      <c r="M2" s="3" t="n">
         <v>143320.11</v>
       </c>
-      <c r="N2" s="14" t="n">
+      <c r="N2" s="3" t="n">
         <v>143320.11</v>
       </c>
-      <c r="O2" s="14" t="n">
+      <c r="O2" s="3" t="n">
         <v>143320.11</v>
       </c>
-      <c r="P2" s="14" t="n">
+      <c r="P2" s="3" t="n">
         <v>143322</v>
       </c>
-      <c r="Q2" s="14">
+      <c r="Q2" s="3">
         <f>SUM(E2:P2)</f>
         <v/>
       </c>
-      <c r="R2" s="14" t="n">
+      <c r="R2" s="3" t="n">
         <v>1627896.99</v>
       </c>
-      <c r="S2" s="14">
+      <c r="S2" s="3">
         <f>Q2-R2</f>
         <v/>
       </c>
@@ -7475,53 +7621,53 @@
           <t>QP</t>
         </is>
       </c>
-      <c r="D3" s="13" t="n">
+      <c r="D3" s="16" t="n">
         <v>46508</v>
       </c>
-      <c r="E3" s="14" t="n">
+      <c r="E3" s="3" t="n">
         <v>66860.11</v>
       </c>
-      <c r="F3" s="14" t="n">
+      <c r="F3" s="3" t="n">
         <v>66860.11</v>
       </c>
-      <c r="G3" s="14" t="n">
+      <c r="G3" s="3" t="n">
         <v>66860.11</v>
       </c>
-      <c r="H3" s="14" t="n">
+      <c r="H3" s="3" t="n">
         <v>66860.11</v>
       </c>
-      <c r="I3" s="14" t="n">
+      <c r="I3" s="3" t="n">
         <v>66860.11</v>
       </c>
-      <c r="J3" s="14" t="n">
+      <c r="J3" s="3" t="n">
         <v>66860.11</v>
       </c>
-      <c r="K3" s="14" t="n">
+      <c r="K3" s="3" t="n">
         <v>66860.11</v>
       </c>
-      <c r="L3" s="14" t="n">
+      <c r="L3" s="3" t="n">
         <v>66860.11</v>
       </c>
-      <c r="M3" s="14" t="n">
+      <c r="M3" s="3" t="n">
         <v>66860.11</v>
       </c>
-      <c r="N3" s="14" t="n">
+      <c r="N3" s="3" t="n">
         <v>66860.11</v>
       </c>
-      <c r="O3" s="14" t="n">
+      <c r="O3" s="3" t="n">
         <v>66860.11</v>
       </c>
-      <c r="P3" s="14" t="n">
+      <c r="P3" s="3" t="n">
         <v>66861.14999999999</v>
       </c>
-      <c r="Q3" s="14">
+      <c r="Q3" s="3">
         <f>SUM(E3:P3)</f>
         <v/>
       </c>
-      <c r="R3" s="14" t="n">
+      <c r="R3" s="3" t="n">
         <v>1083084.59</v>
       </c>
-      <c r="S3" s="14">
+      <c r="S3" s="3">
         <f>Q3-R3</f>
         <v/>
       </c>
@@ -7540,53 +7686,53 @@
           <t>QS</t>
         </is>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="16" t="n">
         <v>46508</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="3" t="n">
         <v>19964.91</v>
       </c>
-      <c r="F4" s="14" t="n">
+      <c r="F4" s="3" t="n">
         <v>19964.91</v>
       </c>
-      <c r="G4" s="14" t="n">
+      <c r="G4" s="3" t="n">
         <v>19964.91</v>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="H4" s="3" t="n">
         <v>19964.91</v>
       </c>
-      <c r="I4" s="14" t="n">
+      <c r="I4" s="3" t="n">
         <v>19964.91</v>
       </c>
-      <c r="J4" s="14" t="n">
+      <c r="J4" s="3" t="n">
         <v>19964.91</v>
       </c>
-      <c r="K4" s="14" t="n">
+      <c r="K4" s="3" t="n">
         <v>19964.91</v>
       </c>
-      <c r="L4" s="14" t="n">
+      <c r="L4" s="3" t="n">
         <v>19964.91</v>
       </c>
-      <c r="M4" s="14" t="n">
+      <c r="M4" s="3" t="n">
         <v>19964.91</v>
       </c>
-      <c r="N4" s="14" t="n">
+      <c r="N4" s="3" t="n">
         <v>19964.91</v>
       </c>
-      <c r="O4" s="14" t="n">
+      <c r="O4" s="3" t="n">
         <v>19964.91</v>
       </c>
-      <c r="P4" s="14" t="n">
+      <c r="P4" s="3" t="n">
         <v>19967.79</v>
       </c>
-      <c r="Q4" s="14">
+      <c r="Q4" s="3">
         <f>SUM(E4:P4)</f>
         <v/>
       </c>
-      <c r="R4" s="14" t="n">
+      <c r="R4" s="3" t="n">
         <v>275195.36</v>
       </c>
-      <c r="S4" s="14">
+      <c r="S4" s="3">
         <f>Q4-R4</f>
         <v/>
       </c>
@@ -7605,53 +7751,53 @@
           <t>QS</t>
         </is>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="16" t="n">
         <v>46508</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="F5" s="14" t="n">
+      <c r="F5" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="G5" s="14" t="n">
+      <c r="G5" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="H5" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="I5" s="14" t="n">
+      <c r="I5" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="J5" s="14" t="n">
+      <c r="J5" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="K5" s="14" t="n">
+      <c r="K5" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="L5" s="14" t="n">
+      <c r="L5" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="M5" s="14" t="n">
+      <c r="M5" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="N5" s="14" t="n">
+      <c r="N5" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="O5" s="14" t="n">
+      <c r="O5" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="P5" s="14" t="n">
+      <c r="P5" s="3" t="n">
         <v>9230.049999999999</v>
       </c>
-      <c r="Q5" s="14">
+      <c r="Q5" s="3">
         <f>SUM(E5:P5)</f>
         <v/>
       </c>
-      <c r="R5" s="14" t="n">
+      <c r="R5" s="3" t="n">
         <v>121831.52</v>
       </c>
-      <c r="S5" s="14">
+      <c r="S5" s="3">
         <f>Q5-R5</f>
         <v/>
       </c>
@@ -7670,53 +7816,53 @@
           <t>QP</t>
         </is>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="16" t="n">
         <v>46539</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="3" t="n">
         <v>33301.1</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="3" t="n">
         <v>33301.1</v>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="G6" s="3" t="n">
         <v>33301.1</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="H6" s="3" t="n">
         <v>33301.1</v>
       </c>
-      <c r="I6" s="14" t="n">
+      <c r="I6" s="3" t="n">
         <v>33301.1</v>
       </c>
-      <c r="J6" s="14" t="n">
+      <c r="J6" s="3" t="n">
         <v>33301.1</v>
       </c>
-      <c r="K6" s="14" t="n">
+      <c r="K6" s="3" t="n">
         <v>33301.1</v>
       </c>
-      <c r="L6" s="14" t="n">
+      <c r="L6" s="3" t="n">
         <v>33301.1</v>
       </c>
-      <c r="M6" s="14" t="n">
+      <c r="M6" s="3" t="n">
         <v>33301.1</v>
       </c>
-      <c r="N6" s="14" t="n">
+      <c r="N6" s="3" t="n">
         <v>33301.1</v>
       </c>
-      <c r="O6" s="14" t="n">
+      <c r="O6" s="3" t="n">
         <v>33301.1</v>
       </c>
-      <c r="P6" s="14" t="n">
+      <c r="P6" s="3" t="n">
         <v>33302.24</v>
       </c>
-      <c r="Q6" s="14">
+      <c r="Q6" s="3">
         <f>SUM(E6:P6)</f>
         <v/>
       </c>
-      <c r="R6" s="14" t="n">
+      <c r="R6" s="3" t="n">
         <v>539995.52</v>
       </c>
-      <c r="S6" s="14">
+      <c r="S6" s="3">
         <f>Q6-R6</f>
         <v/>
       </c>
@@ -7735,53 +7881,53 @@
           <t>QP</t>
         </is>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="16" t="n">
         <v>46539</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="3" t="n">
         <v>33326.04</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="3" t="n">
         <v>33326.04</v>
       </c>
-      <c r="G7" s="14" t="n">
+      <c r="G7" s="3" t="n">
         <v>33326.04</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="H7" s="3" t="n">
         <v>33326.04</v>
       </c>
-      <c r="I7" s="14" t="n">
+      <c r="I7" s="3" t="n">
         <v>33326.04</v>
       </c>
-      <c r="J7" s="14" t="n">
+      <c r="J7" s="3" t="n">
         <v>33326.04</v>
       </c>
-      <c r="K7" s="14" t="n">
+      <c r="K7" s="3" t="n">
         <v>33326.04</v>
       </c>
-      <c r="L7" s="14" t="n">
+      <c r="L7" s="3" t="n">
         <v>33326.04</v>
       </c>
-      <c r="M7" s="14" t="n">
+      <c r="M7" s="3" t="n">
         <v>33326.04</v>
       </c>
-      <c r="N7" s="14" t="n">
+      <c r="N7" s="3" t="n">
         <v>33326.04</v>
       </c>
-      <c r="O7" s="14" t="n">
+      <c r="O7" s="3" t="n">
         <v>33326.04</v>
       </c>
-      <c r="P7" s="14" t="n">
+      <c r="P7" s="3" t="n">
         <v>33327.28</v>
       </c>
-      <c r="Q7" s="14">
+      <c r="Q7" s="3">
         <f>SUM(E7:P7)</f>
         <v/>
       </c>
-      <c r="R7" s="14" t="n">
+      <c r="R7" s="3" t="n">
         <v>540294.9</v>
       </c>
-      <c r="S7" s="14">
+      <c r="S7" s="3">
         <f>Q7-R7</f>
         <v/>
       </c>
@@ -7800,53 +7946,53 @@
           <t>QS</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="16" t="n">
         <v>46539</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="3" t="n">
         <v>32562.34</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="3" t="n">
         <v>32562.34</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="3" t="n">
         <v>32562.34</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="H8" s="3" t="n">
         <v>32562.34</v>
       </c>
-      <c r="I8" s="14" t="n">
+      <c r="I8" s="3" t="n">
         <v>32562.34</v>
       </c>
-      <c r="J8" s="14" t="n">
+      <c r="J8" s="3" t="n">
         <v>32562.34</v>
       </c>
-      <c r="K8" s="14" t="n">
+      <c r="K8" s="3" t="n">
         <v>32562.34</v>
       </c>
-      <c r="L8" s="14" t="n">
+      <c r="L8" s="3" t="n">
         <v>32562.34</v>
       </c>
-      <c r="M8" s="14" t="n">
+      <c r="M8" s="3" t="n">
         <v>32562.34</v>
       </c>
-      <c r="N8" s="14" t="n">
+      <c r="N8" s="3" t="n">
         <v>32562.34</v>
       </c>
-      <c r="O8" s="14" t="n">
+      <c r="O8" s="3" t="n">
         <v>32562.34</v>
       </c>
-      <c r="P8" s="14" t="n">
+      <c r="P8" s="3" t="n">
         <v>32564.29</v>
       </c>
-      <c r="Q8" s="14">
+      <c r="Q8" s="3">
         <f>SUM(E8:P8)</f>
         <v/>
       </c>
-      <c r="R8" s="14" t="n">
+      <c r="R8" s="3" t="n">
         <v>505316.58</v>
       </c>
-      <c r="S8" s="14">
+      <c r="S8" s="3">
         <f>Q8-R8</f>
         <v/>
       </c>
@@ -7865,53 +8011,53 @@
           <t>QS</t>
         </is>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="16" t="n">
         <v>46539</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="3" t="n">
         <v>10853.96</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="3" t="n">
         <v>10853.96</v>
       </c>
-      <c r="G9" s="14" t="n">
+      <c r="G9" s="3" t="n">
         <v>10853.96</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="H9" s="3" t="n">
         <v>10853.96</v>
       </c>
-      <c r="I9" s="14" t="n">
+      <c r="I9" s="3" t="n">
         <v>10853.96</v>
       </c>
-      <c r="J9" s="14" t="n">
+      <c r="J9" s="3" t="n">
         <v>10853.96</v>
       </c>
-      <c r="K9" s="14" t="n">
+      <c r="K9" s="3" t="n">
         <v>10853.96</v>
       </c>
-      <c r="L9" s="14" t="n">
+      <c r="L9" s="3" t="n">
         <v>10853.96</v>
       </c>
-      <c r="M9" s="14" t="n">
+      <c r="M9" s="3" t="n">
         <v>10853.96</v>
       </c>
-      <c r="N9" s="14" t="n">
+      <c r="N9" s="3" t="n">
         <v>10853.96</v>
       </c>
-      <c r="O9" s="14" t="n">
+      <c r="O9" s="3" t="n">
         <v>10853.96</v>
       </c>
-      <c r="P9" s="14" t="n">
+      <c r="P9" s="3" t="n">
         <v>10856.4</v>
       </c>
-      <c r="Q9" s="14">
+      <c r="Q9" s="3">
         <f>SUM(E9:P9)</f>
         <v/>
       </c>
-      <c r="R9" s="14" t="n">
+      <c r="R9" s="3" t="n">
         <v>168438.86</v>
       </c>
-      <c r="S9" s="14">
+      <c r="S9" s="3">
         <f>Q9-R9</f>
         <v/>
       </c>
@@ -7930,53 +8076,53 @@
           <t>QS</t>
         </is>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="16" t="n">
         <v>46539</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="G10" s="14" t="n">
+      <c r="G10" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="H10" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="I10" s="14" t="n">
+      <c r="I10" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="J10" s="14" t="n">
+      <c r="J10" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="K10" s="14" t="n">
+      <c r="K10" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="L10" s="14" t="n">
+      <c r="L10" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="M10" s="14" t="n">
+      <c r="M10" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="N10" s="14" t="n">
+      <c r="N10" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="O10" s="14" t="n">
+      <c r="O10" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="P10" s="14" t="n">
+      <c r="P10" s="3" t="n">
         <v>9230.049999999999</v>
       </c>
-      <c r="Q10" s="14">
+      <c r="Q10" s="3">
         <f>SUM(E10:P10)</f>
         <v/>
       </c>
-      <c r="R10" s="14" t="n">
+      <c r="R10" s="3" t="n">
         <v>121831.52</v>
       </c>
-      <c r="S10" s="14">
+      <c r="S10" s="3">
         <f>Q10-R10</f>
         <v/>
       </c>
@@ -7995,53 +8141,53 @@
           <t>QS</t>
         </is>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="16" t="n">
         <v>46539</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="G11" s="14" t="n">
+      <c r="G11" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="H11" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="I11" s="14" t="n">
+      <c r="I11" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="J11" s="14" t="n">
+      <c r="J11" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="K11" s="14" t="n">
+      <c r="K11" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="L11" s="14" t="n">
+      <c r="L11" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="M11" s="14" t="n">
+      <c r="M11" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="N11" s="14" t="n">
+      <c r="N11" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="O11" s="14" t="n">
+      <c r="O11" s="3" t="n">
         <v>9227.84</v>
       </c>
-      <c r="P11" s="14" t="n">
+      <c r="P11" s="3" t="n">
         <v>9230.049999999999</v>
       </c>
-      <c r="Q11" s="14">
+      <c r="Q11" s="3">
         <f>SUM(E11:P11)</f>
         <v/>
       </c>
-      <c r="R11" s="14" t="n">
+      <c r="R11" s="3" t="n">
         <v>121831.52</v>
       </c>
-      <c r="S11" s="14">
+      <c r="S11" s="3">
         <f>Q11-R11</f>
         <v/>
       </c>
@@ -8060,53 +8206,53 @@
           <t>QP</t>
         </is>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="16" t="n">
         <v>46600</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="3" t="n">
         <v>33301.1</v>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="3" t="n">
         <v>33301.1</v>
       </c>
-      <c r="G12" s="14" t="n">
+      <c r="G12" s="3" t="n">
         <v>33301.1</v>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="H12" s="3" t="n">
         <v>33301.1</v>
       </c>
-      <c r="I12" s="14" t="n">
+      <c r="I12" s="3" t="n">
         <v>33301.1</v>
       </c>
-      <c r="J12" s="14" t="n">
+      <c r="J12" s="3" t="n">
         <v>33301.1</v>
       </c>
-      <c r="K12" s="14" t="n">
+      <c r="K12" s="3" t="n">
         <v>33301.1</v>
       </c>
-      <c r="L12" s="14" t="n">
+      <c r="L12" s="3" t="n">
         <v>33301.1</v>
       </c>
-      <c r="M12" s="14" t="n">
+      <c r="M12" s="3" t="n">
         <v>33301.1</v>
       </c>
-      <c r="N12" s="14" t="n">
+      <c r="N12" s="3" t="n">
         <v>33301.1</v>
       </c>
-      <c r="O12" s="14" t="n">
+      <c r="O12" s="3" t="n">
         <v>33301.1</v>
       </c>
-      <c r="P12" s="14" t="n">
+      <c r="P12" s="3" t="n">
         <v>33302.24</v>
       </c>
-      <c r="Q12" s="14">
+      <c r="Q12" s="3">
         <f>SUM(E12:P12)</f>
         <v/>
       </c>
-      <c r="R12" s="14" t="n">
+      <c r="R12" s="3" t="n">
         <v>539995.52</v>
       </c>
-      <c r="S12" s="14">
+      <c r="S12" s="3">
         <f>Q12-R12</f>
         <v/>
       </c>
@@ -8125,137 +8271,138 @@
           <t>QP</t>
         </is>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="16" t="n">
         <v>46600</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="3" t="n">
         <v>27582.14</v>
       </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="3" t="n">
         <v>27582.14</v>
       </c>
-      <c r="G13" s="14" t="n">
+      <c r="G13" s="3" t="n">
         <v>27582.14</v>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="H13" s="3" t="n">
         <v>27582.14</v>
       </c>
-      <c r="I13" s="14" t="n">
+      <c r="I13" s="3" t="n">
         <v>27582.14</v>
       </c>
-      <c r="J13" s="14" t="n">
+      <c r="J13" s="3" t="n">
         <v>27582.14</v>
       </c>
-      <c r="K13" s="14" t="n">
+      <c r="K13" s="3" t="n">
         <v>27582.14</v>
       </c>
-      <c r="L13" s="14" t="n">
+      <c r="L13" s="3" t="n">
         <v>27582.14</v>
       </c>
-      <c r="M13" s="14" t="n">
+      <c r="M13" s="3" t="n">
         <v>27582.14</v>
       </c>
-      <c r="N13" s="14" t="n">
+      <c r="N13" s="3" t="n">
         <v>27582.14</v>
       </c>
-      <c r="O13" s="14" t="n">
+      <c r="O13" s="3" t="n">
         <v>27582.14</v>
       </c>
-      <c r="P13" s="14" t="n">
+      <c r="P13" s="3" t="n">
         <v>27585.47</v>
       </c>
-      <c r="Q13" s="14">
+      <c r="Q13" s="3">
         <f>SUM(E13:P13)</f>
         <v/>
       </c>
-      <c r="R13" s="14" t="n">
+      <c r="R13" s="3" t="n">
         <v>373175.86</v>
       </c>
-      <c r="S13" s="14">
+      <c r="S13" s="3">
         <f>Q13-R13</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="15" t="inlineStr"/>
-      <c r="E14" s="16">
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="17" t="inlineStr"/>
+      <c r="E14" s="18">
         <f>SUM(E2:E13)</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="18">
         <f>SUM(F2:F13)</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="18">
         <f>SUM(G2:G13)</f>
         <v/>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="18">
         <f>SUM(H2:H13)</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="18">
         <f>SUM(I2:I13)</f>
         <v/>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="18">
         <f>SUM(J2:J13)</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="18">
         <f>SUM(K2:K13)</f>
         <v/>
       </c>
-      <c r="L14" s="16">
+      <c r="L14" s="18">
         <f>SUM(L2:L13)</f>
         <v/>
       </c>
-      <c r="M14" s="16">
+      <c r="M14" s="18">
         <f>SUM(M2:M13)</f>
         <v/>
       </c>
-      <c r="N14" s="16">
+      <c r="N14" s="18">
         <f>SUM(N2:N13)</f>
         <v/>
       </c>
-      <c r="O14" s="16">
+      <c r="O14" s="18">
         <f>SUM(O2:O13)</f>
         <v/>
       </c>
-      <c r="P14" s="16">
+      <c r="P14" s="18">
         <f>SUM(P2:P13)</f>
         <v/>
       </c>
-      <c r="Q14" s="16">
+      <c r="Q14" s="18">
         <f>SUM(Q2:Q13)</f>
         <v/>
       </c>
-      <c r="R14" s="16">
+      <c r="R14" s="18">
         <f>SUM(R2:R13)</f>
         <v/>
       </c>
-      <c r="S14" s="16">
+      <c r="S14" s="18">
         <f>Q14-R14</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -8267,22 +8414,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Etapa do BLOCO (equipamento especial RL / RT / BC)</t>
         </is>
       </c>
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Duração padrão</t>
         </is>
       </c>
-      <c r="C1" s="17" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Unidade</t>
         </is>
       </c>
-      <c r="D1" s="17" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Origem</t>
         </is>
@@ -8484,5 +8631,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>